--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
         <v>2.36</v>
       </c>
       <c r="I3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
         <v>2.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,498 +843,752 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Academia de Balompie Bo</t>
+          <t>Valerenga</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Independiente Petr</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Academia de Balompie Bo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Club Independiente Petr</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K3" t="n">
+        <v>950</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>18:30:00</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Aucas</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="F4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.2</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="K4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-07-14 13:57:32</t>
+      <c r="Q4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -872,7 +872,7 @@
         <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.22</v>
@@ -896,7 +896,7 @@
         <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
@@ -917,7 +917,7 @@
         <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
         <v>110</v>
@@ -968,7 +968,7 @@
         <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
         <v>4.4</v>
@@ -1010,7 +1010,7 @@
         <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
         <v>5.3</v>
@@ -1022,25 +1022,25 @@
         <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN2" t="n">
         <v>5</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP2" t="n">
         <v>11.5</v>
@@ -1049,25 +1049,25 @@
         <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
         <v>8.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX2" t="n">
         <v>32</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>34</v>
       </c>
       <c r="BY2" t="n">
         <v>10</v>
@@ -1076,11 +1076,11 @@
         <v>13</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -1111,46 +1111,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.13</v>
       </c>
       <c r="P3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.29</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
         <v>2.3</v>
@@ -1398,7 +1398,7 @@
         <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G2" t="n">
         <v>1.83</v>
@@ -890,16 +890,16 @@
         <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
         <v>2.54</v>
@@ -911,7 +911,7 @@
         <v>1.99</v>
       </c>
       <c r="X2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
         <v>32</v>
@@ -923,7 +923,7 @@
         <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
         <v>13</v>
@@ -938,7 +938,7 @@
         <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>19.5</v>
@@ -965,16 +965,16 @@
         <v>40</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
         <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
@@ -986,7 +986,7 @@
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
         <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
         <v>17.5</v>
@@ -1010,28 +1010,28 @@
         <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF2" t="n">
         <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
         <v>5.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM2" t="n">
         <v>12.5</v>
@@ -1040,19 +1040,19 @@
         <v>5</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>19.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
         <v>8.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>1.05</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1141,7 +1141,7 @@
         <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Q3" t="n">
         <v>1.13</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
         <v>3.65</v>
@@ -1374,7 +1374,7 @@
         <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
@@ -1383,16 +1383,16 @@
         <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
         <v>1.78</v>
@@ -1401,194 +1401,1210 @@
         <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EC Vitoria Salvador</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>44</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-07-14 20:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Botafogo FR</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-14 20:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>19</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-14 20:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Forge</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,7 +899,7 @@
         <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
         <v>2.54</v>
@@ -1028,13 +1028,13 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN2" t="n">
         <v>5</v>
@@ -1043,44 +1043,44 @@
         <v>4.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>19.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>8.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV2" t="n">
         <v>30</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
         <v>32</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
         <v>100</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>130</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>950</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.15</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.86</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.37</v>
+        <v>2.76</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>2.56</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
         <v>14</v>
       </c>
-      <c r="Z5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BX5" t="n">
         <v>48</v>
       </c>
-      <c r="AP5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>55</v>
-      </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -1864,97 +1864,97 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="H6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.8</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>18.5</v>
@@ -1963,147 +1963,147 @@
         <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
         <v>46</v>
       </c>
       <c r="AP6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="AY6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD6" t="n">
         <v>38</v>
       </c>
-      <c r="AX6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>30</v>
-      </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BG6" t="n">
         <v>34</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BW6" t="n">
         <v>10.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,498 +2113,1006 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
         <v>30</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO7" t="n">
         <v>46</v>
       </c>
-      <c r="AM7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>80</v>
-      </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="BC7" t="n">
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BE7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN7" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP7" t="n">
         <v>15</v>
       </c>
       <c r="BQ7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
+      <c r="BX7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>24</v>
       </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA7" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-14 22:29:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Forge</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Pacific</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>1.24</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="G9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.15</v>
       </c>
-      <c r="I8" t="n">
-        <v>17</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="P9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-14 22:29:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.28</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-14 20:21:48</t>
+      <c r="Q10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X10" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
         <v>1.83</v>
@@ -1046,7 +1046,7 @@
         <v>11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR2" t="n">
         <v>19.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>5.7</v>
       </c>
       <c r="I4" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="J4" t="n">
         <v>5.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
         <v>3.25</v>
@@ -1685,7 +1685,7 @@
         <v>36</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
@@ -1763,16 +1763,16 @@
         <v>4.8</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC5" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
         <v>4.8</v>
@@ -1784,7 +1784,7 @@
         <v>3.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="BJ5" t="n">
         <v>14.5</v>
@@ -1802,7 +1802,7 @@
         <v>9</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
         <v>40</v>
@@ -1820,7 +1820,7 @@
         <v>7.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BV5" t="n">
         <v>26</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1924,16 +1924,16 @@
         <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
         <v>60</v>
@@ -1942,7 +1942,7 @@
         <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>17.5</v>
@@ -1966,7 +1966,7 @@
         <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -1978,7 +1978,7 @@
         <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP6" t="n">
         <v>11</v>
@@ -1987,7 +1987,7 @@
         <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
         <v>50</v>
@@ -2002,7 +2002,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
@@ -2014,10 +2014,10 @@
         <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
         <v>24</v>
@@ -2026,7 +2026,7 @@
         <v>38</v>
       </c>
       <c r="BE6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>2.12</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
         <v>4.1</v>
@@ -2145,7 +2145,7 @@
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2160,7 +2160,7 @@
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
         <v>1.38</v>
@@ -2229,7 +2229,7 @@
         <v>100</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>46</v>
@@ -2244,7 +2244,7 @@
         <v>25</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
         <v>9.4</v>
@@ -2268,7 +2268,7 @@
         <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
         <v>22</v>
@@ -2280,7 +2280,7 @@
         <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
         <v>13</v>
@@ -2292,10 +2292,10 @@
         <v>3.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK7" t="n">
         <v>6</v>
@@ -2304,25 +2304,25 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN7" t="n">
         <v>4.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
         <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT7" t="n">
         <v>7.2</v>
@@ -2334,23 +2334,23 @@
         <v>32</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ7" t="n">
         <v>24</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
         <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
         <v>1.42</v>
@@ -2405,7 +2405,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.34</v>
@@ -2417,55 +2417,55 @@
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
         <v>3.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
         <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
         <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
         <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
         <v>80</v>
@@ -2474,7 +2474,7 @@
         <v>29</v>
       </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
         <v>44</v>
@@ -2492,13 +2492,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
         <v>7.8</v>
@@ -2507,10 +2507,10 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2522,25 +2522,25 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BC8" t="n">
         <v>19</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="n">
         <v>3.35</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>17</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="K9" t="n">
         <v>7.8</v>
@@ -2665,7 +2665,7 @@
         <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
         <v>1.46</v>
@@ -2686,7 +2686,7 @@
         <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -2895,10 +2895,10 @@
         <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J10" t="n">
         <v>3.85</v>
@@ -2913,22 +2913,22 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
         <v>1.6</v>
@@ -2958,7 +2958,7 @@
         <v>15</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
         <v>18.5</v>
@@ -3006,7 +3006,7 @@
         <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -3042,7 +3042,7 @@
         <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
         <v>8.199999999999999</v>
@@ -3099,7 +3099,7 @@
         <v>18</v>
       </c>
       <c r="BX10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY10" t="n">
         <v>22</v>
@@ -3112,7 +3112,1277 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>48</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>St Louis City SC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X15" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -860,7 +860,7 @@
         <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
@@ -869,7 +869,7 @@
         <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.6</v>
@@ -887,13 +887,13 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S2" t="n">
         <v>2.26</v>
@@ -902,7 +902,7 @@
         <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
@@ -965,13 +965,13 @@
         <v>40</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
         <v>4.8</v>
@@ -983,40 +983,40 @@
         <v>9.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
         <v>17.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
         <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.34</v>
@@ -1709,7 +1709,7 @@
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
         <v>50</v>
@@ -1748,7 +1748,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
         <v>19.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
         <v>1.45</v>
@@ -1900,16 +1900,16 @@
         <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
         <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
         <v>3.8</v>
@@ -1921,10 +1921,10 @@
         <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -1945,10 +1945,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
         <v>15.5</v>
@@ -2002,7 +2002,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
@@ -2044,7 +2044,7 @@
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2065,7 +2065,7 @@
         <v>9</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS6" t="n">
         <v>11.5</v>
@@ -2077,7 +2077,7 @@
         <v>5.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
         <v>10.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
         <v>2.12</v>
@@ -2136,7 +2136,7 @@
         <v>3.85</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
@@ -2160,7 +2160,7 @@
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
         <v>1.38</v>
@@ -2271,7 +2271,7 @@
         <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>19</v>
@@ -2292,19 +2292,19 @@
         <v>3.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN7" t="n">
         <v>4.9</v>
@@ -2316,13 +2316,13 @@
         <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT7" t="n">
         <v>7.2</v>
@@ -2331,26 +2331,26 @@
         <v>5.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX7" t="n">
         <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>24</v>
       </c>
       <c r="CA7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
         <v>4.3</v>
@@ -2417,7 +2417,7 @@
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
         <v>3.55</v>
@@ -2429,7 +2429,7 @@
         <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.9</v>
@@ -2453,7 +2453,7 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
         <v>70</v>
@@ -2471,7 +2471,7 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
         <v>23</v>
@@ -2483,7 +2483,7 @@
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO8" t="n">
         <v>80</v>
@@ -2495,10 +2495,10 @@
         <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
         <v>7.8</v>
@@ -2510,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2522,25 +2522,25 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC8" t="n">
         <v>19</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.35</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.31</v>
@@ -2967,10 +2967,10 @@
         <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
@@ -3003,13 +3003,13 @@
         <v>15.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU10" t="n">
         <v>8.199999999999999</v>
@@ -3018,10 +3018,10 @@
         <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
         <v>9.4</v>
@@ -3030,7 +3030,7 @@
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
         <v>18.5</v>
@@ -3042,7 +3042,7 @@
         <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
         <v>8.199999999999999</v>
@@ -3069,7 +3069,7 @@
         <v>21</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
         <v>4.3</v>
@@ -3164,7 +3164,7 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
         <v>2.96</v>
@@ -3215,10 +3215,10 @@
         <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
         <v>14.5</v>
@@ -3227,10 +3227,10 @@
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
         <v>30</v>
@@ -3257,22 +3257,22 @@
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW11" t="n">
         <v>6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.9</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3281,92 +3281,92 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BJ11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BO11" t="n">
         <v>3.35</v>
       </c>
       <c r="BP11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BR11" t="n">
         <v>48</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BT11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BZ11" t="n">
         <v>48</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I12" t="n">
         <v>2.46</v>
@@ -3421,19 +3421,19 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q12" t="n">
         <v>1.57</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S12" t="n">
         <v>2.42</v>
@@ -3445,7 +3445,7 @@
         <v>2.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W12" t="n">
         <v>1.5</v>
@@ -3499,13 +3499,13 @@
         <v>65</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ12" t="n">
         <v>14</v>
@@ -3514,7 +3514,7 @@
         <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT12" t="n">
         <v>15</v>
@@ -3523,7 +3523,7 @@
         <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
         <v>19</v>
@@ -3532,25 +3532,25 @@
         <v>19</v>
       </c>
       <c r="AY12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC12" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
         <v>12</v>
@@ -3559,16 +3559,16 @@
         <v>10.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,50 +3577,50 @@
         <v>21</v>
       </c>
       <c r="BN12" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BQ12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BR12" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BS12" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BV12" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BX12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BY12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BZ12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="CA12" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3657,13 @@
         <v>1.49</v>
       </c>
       <c r="H13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K13" t="n">
         <v>5.7</v>
@@ -3696,10 +3696,10 @@
         <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -3741,7 +3741,7 @@
         <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
         <v>14.5</v>
@@ -3753,7 +3753,7 @@
         <v>90</v>
       </c>
       <c r="AN13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO13" t="n">
         <v>75</v>
@@ -3765,10 +3765,10 @@
         <v>25</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT13" t="n">
         <v>12</v>
@@ -3780,7 +3780,7 @@
         <v>19.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3792,7 +3792,7 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
         <v>12.5</v>
@@ -3804,13 +3804,13 @@
         <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
         <v>4.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH13" t="n">
         <v>5.4</v>
@@ -3837,7 +3837,7 @@
         <v>4</v>
       </c>
       <c r="BP13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ13" t="n">
         <v>6.2</v>
@@ -3849,7 +3849,7 @@
         <v>12</v>
       </c>
       <c r="BT13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU13" t="n">
         <v>7.4</v>
@@ -3867,14 +3867,14 @@
         <v>21</v>
       </c>
       <c r="BZ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA13" t="n">
         <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>3.9</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>3.8</v>
@@ -3935,34 +3935,34 @@
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R14" t="n">
         <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
         <v>1.96</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="n">
         <v>36</v>
@@ -3977,130 +3977,130 @@
         <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK14" t="n">
         <v>23</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP14" t="n">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="AV14" t="n">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="AY14" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="BH14" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.74</v>
+        <v>1.99</v>
       </c>
       <c r="BJ14" t="n">
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.62</v>
+        <v>1.72</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>3.3</v>
+        <v>1.99</v>
       </c>
       <c r="BN14" t="n">
         <v>6.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP14" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="BR14" t="n">
         <v>34</v>
       </c>
       <c r="BS14" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="BT14" t="n">
         <v>10</v>
@@ -4112,23 +4112,23 @@
         <v>44</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.05</v>
+        <v>1.91</v>
       </c>
       <c r="BX14" t="n">
         <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="BZ14" t="n">
         <v>28</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.96</v>
+        <v>1.86</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I15" t="n">
         <v>6.8</v>
@@ -4177,25 +4177,25 @@
         <v>5.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
         <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S15" t="n">
         <v>2.08</v>
@@ -4204,22 +4204,22 @@
         <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
         <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X15" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Y15" t="n">
         <v>36</v>
       </c>
       <c r="Z15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA15" t="n">
         <v>170</v>
@@ -4234,7 +4234,7 @@
         <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF15" t="n">
         <v>13.5</v>
@@ -4246,7 +4246,7 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
         <v>16.5</v>
@@ -4258,25 +4258,25 @@
         <v>25</v>
       </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
         <v>12</v>
@@ -4288,7 +4288,7 @@
         <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX15" t="n">
         <v>10.5</v>
@@ -4300,7 +4300,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
@@ -4312,19 +4312,19 @@
         <v>20</v>
       </c>
       <c r="BE15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH15" t="n">
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
         <v>13.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.22</v>
@@ -887,16 +887,16 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
         <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
@@ -908,7 +908,7 @@
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
         <v>34</v>
@@ -959,34 +959,34 @@
         <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
         <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2" t="n">
         <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,7 +998,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
         <v>17.5</v>
@@ -1010,16 +1010,16 @@
         <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI2" t="n">
         <v>4.1</v>
@@ -1028,13 +1028,13 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
         <v>5</v>
@@ -1049,22 +1049,22 @@
         <v>8.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>8.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV2" t="n">
         <v>30</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>32</v>
@@ -1076,11 +1076,11 @@
         <v>12.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="I4" t="n">
-        <v>110</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="R4" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="S4" t="n">
         <v>1.83</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AV4" t="n">
         <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="n">
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>2.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
@@ -1643,7 +1643,7 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.34</v>
@@ -1676,7 +1676,7 @@
         <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
         <v>16</v>
@@ -1736,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
         <v>19.5</v>
@@ -1760,28 +1760,28 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG5" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
         <v>1.78</v>
@@ -1790,59 +1790,59 @@
         <v>14.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>2.66</v>
+        <v>1.58</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.25</v>
+        <v>1.78</v>
       </c>
       <c r="BN5" t="n">
         <v>9</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
         <v>40</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="BT5" t="n">
         <v>7.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV5" t="n">
         <v>26</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="BX5" t="n">
         <v>48</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.05</v>
+        <v>1.72</v>
       </c>
       <c r="BZ5" t="n">
         <v>46</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.05</v>
+        <v>1.71</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
         <v>3.25</v>
@@ -1942,13 +1942,13 @@
         <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF6" t="n">
         <v>15.5</v>
@@ -1975,7 +1975,7 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
         <v>42</v>
@@ -1987,7 +1987,7 @@
         <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AS6" t="n">
         <v>50</v>
@@ -2002,7 +2002,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
@@ -2017,7 +2017,7 @@
         <v>46</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC6" t="n">
         <v>24</v>
@@ -2032,13 +2032,13 @@
         <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH6" t="n">
         <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5.3</v>
@@ -2062,16 +2062,16 @@
         <v>19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR6" t="n">
         <v>34</v>
       </c>
       <c r="BS6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
         <v>5.6</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX6" t="n">
         <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G7" t="n">
         <v>2.12</v>
@@ -2136,7 +2136,7 @@
         <v>3.85</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
@@ -2405,13 +2405,13 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
         <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -2420,7 +2420,7 @@
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
         <v>1.8</v>
@@ -2429,7 +2429,7 @@
         <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
         <v>1.9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>1.32</v>
       </c>
       <c r="H9" t="n">
-        <v>7.8</v>
+        <v>1.49</v>
       </c>
       <c r="I9" t="n">
         <v>17</v>
@@ -2653,16 +2653,16 @@
         <v>7.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.66</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
         <v>2.58</v>
@@ -2671,76 +2671,76 @@
         <v>1.46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
         <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP9" t="n">
         <v>1.03</v>
@@ -2791,22 +2791,22 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG9" t="n">
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2815,28 +2815,28 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2851,14 +2851,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
         <v>1.67</v>
@@ -3051,7 +3051,7 @@
         <v>19.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI10" t="n">
         <v>3.3</v>
@@ -3060,22 +3060,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>85</v>
       </c>
       <c r="BM10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO10" t="n">
         <v>4</v>
       </c>
       <c r="BP10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>10</v>
@@ -3090,7 +3090,7 @@
         <v>7.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV10" t="n">
         <v>26</v>
@@ -3099,7 +3099,7 @@
         <v>18</v>
       </c>
       <c r="BX10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY10" t="n">
         <v>22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -3218,7 +3218,7 @@
         <v>19.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF11" t="n">
         <v>14.5</v>
@@ -3230,7 +3230,7 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="n">
         <v>30</v>
@@ -3251,7 +3251,7 @@
         <v>90</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
@@ -3263,13 +3263,13 @@
         <v>6.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU11" t="n">
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
         <v>6</v>
@@ -3281,13 +3281,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
         <v>5.4</v>
@@ -3302,71 +3302,71 @@
         <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.82</v>
+        <v>2.52</v>
       </c>
       <c r="BJ11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.63</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.82</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU11" t="n">
         <v>6</v>
       </c>
-      <c r="BO11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.77</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.78</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.76</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I12" t="n">
         <v>2.46</v>
@@ -3421,22 +3421,22 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
         <v>1.57</v>
       </c>
       <c r="R12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
         <v>1.52</v>
@@ -3445,7 +3445,7 @@
         <v>2.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W12" t="n">
         <v>1.5</v>
@@ -3499,13 +3499,13 @@
         <v>65</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO12" t="n">
         <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>14</v>
@@ -3547,7 +3547,7 @@
         <v>4.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
         <v>4.7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.47</v>
       </c>
       <c r="G13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H13" t="n">
         <v>7</v>
@@ -3663,10 +3663,10 @@
         <v>7.6</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.23</v>
@@ -3681,13 +3681,13 @@
         <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
         <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S13" t="n">
         <v>2.08</v>
@@ -3702,7 +3702,7 @@
         <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X13" t="n">
         <v>38</v>
@@ -3792,7 +3792,7 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB13" t="n">
         <v>12.5</v>
@@ -3804,13 +3804,13 @@
         <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
         <v>4.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="n">
         <v>5.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G14" t="n">
         <v>2.04</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I14" t="n">
         <v>4.3</v>
@@ -3923,7 +3923,7 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3938,16 +3938,16 @@
         <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R14" t="n">
         <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
         <v>2.08</v>
@@ -3959,10 +3959,10 @@
         <v>1.96</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z14" t="n">
         <v>36</v>
@@ -3977,7 +3977,7 @@
         <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE14" t="n">
         <v>55</v>
@@ -3992,7 +3992,7 @@
         <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
         <v>27</v>
@@ -4001,134 +4001,134 @@
         <v>23</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="AY14" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO14" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BP14" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR14" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.88</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV14" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.91</v>
+        <v>10.5</v>
       </c>
       <c r="BX14" t="n">
         <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.92</v>
+        <v>11</v>
       </c>
       <c r="BZ14" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.86</v>
+        <v>9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
         <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
         <v>7.2</v>
@@ -4192,7 +4192,7 @@
         <v>3.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
         <v>1.86</v>
@@ -4315,7 +4315,7 @@
         <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
         <v>8.199999999999999</v>
@@ -4342,7 +4342,7 @@
         <v>6.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BP15" t="n">
         <v>13</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Ecuadorian Serie B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Valerenga</t>
+          <t>Cumbaya FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Club Nueve de Octubre</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
         <v>1.03</v>
       </c>
-      <c r="N2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Academia de Balompie Bo</t>
+          <t>Valerenga</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Club Independiente Petr</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>1.81</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>1.29</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.13</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>1.13</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,126 +1351,126 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Academia de Balompie Bo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Club Independiente Petr</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1.43</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.35</v>
+        <v>1.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>1.83</v>
+        <v>1.13</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
         <v>1.01</v>
@@ -1485,117 +1485,117 @@
         <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
         <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
         <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
         <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P5" t="n">
         <v>3.15</v>
       </c>
-      <c r="G5" t="n">
+      <c r="Q5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO5" t="n">
         <v>3.65</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="BP5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="BQ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT5" t="n">
         <v>13</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO5" t="n">
+      <c r="BU5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="CA5" t="n">
         <v>4.6</v>
       </c>
-      <c r="BP5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>46</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1.71</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>14</v>
       </c>
       <c r="AE6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>46</v>
       </c>
-      <c r="AF6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA6" t="n">
-        <v>11.5</v>
+        <v>1.71</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2118,97 +2118,97 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2.08</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.95</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>18.5</v>
@@ -2217,147 +2217,147 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG7" t="n">
         <v>30</v>
       </c>
-      <c r="AK7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="BH7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP7" t="n">
         <v>25</v>
       </c>
-      <c r="AS7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="BQ7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
         <v>12</v>
       </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK7" t="n">
+      <c r="BT7" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BU7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
         <v>12.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,189 +2367,189 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
         <v>2.12</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.9</v>
-      </c>
       <c r="X8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD8" t="n">
         <v>16</v>
       </c>
-      <c r="Y8" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
       <c r="AE8" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU8" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU8" t="n">
-        <v>7</v>
-      </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
         <v>6.2</v>
@@ -2558,60 +2558,60 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS8" t="n">
         <v>11</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW8" t="n">
         <v>11.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
         <v>12.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA8" t="n">
         <v>10.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
-        <v>1.49</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>2.58</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>3.85</v>
+        <v>1.9</v>
       </c>
       <c r="X9" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>570</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>13</v>
       </c>
-      <c r="AC9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AR9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>7</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.04</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="U10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X10" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4.1</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X10" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="BO10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>10</v>
       </c>
-      <c r="AD10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>85</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>18</v>
-      </c>
       <c r="CA10" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US MLS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>CF Montreal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Toronto FC</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.89</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.79</v>
-      </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AJ11" t="n">
         <v>30</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>10</v>
       </c>
-      <c r="AR11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BR11" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BT11" t="n">
         <v>7.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BX11" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BZ11" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
         <v>4.1</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.44</v>
-      </c>
       <c r="T12" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>2.66</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z12" t="n">
         <v>32</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>19.5</v>
       </c>
-      <c r="Z12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>10</v>
       </c>
-      <c r="AD12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI12" t="n">
+      <c r="AR12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD12" t="n">
         <v>36</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="BE12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX12" t="n">
         <v>55</v>
       </c>
-      <c r="AK12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>24</v>
-      </c>
       <c r="BY12" t="n">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="CA12" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>St Louis City SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.47</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>1.48</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>2.38</v>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK13" t="n">
         <v>7.2</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BL13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
         <v>21</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="BQ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT13" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>11</v>
-      </c>
       <c r="BU13" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BV13" t="n">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BX13" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="BY13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BZ13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>US MLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>St Louis City SC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.93</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="H14" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>2.08</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.96</v>
+        <v>3.05</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="Y14" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="Z14" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AM14" t="n">
         <v>90</v>
       </c>
       <c r="AN14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AU14" t="n">
-        <v>3.75</v>
+        <v>12</v>
       </c>
       <c r="AV14" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.6</v>
+        <v>48</v>
       </c>
       <c r="AX14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.8</v>
+        <v>29</v>
       </c>
       <c r="BB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD14" t="n">
         <v>20</v>
       </c>
-      <c r="BC14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>10</v>
-      </c>
       <c r="BE14" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BF14" t="n">
         <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.6</v>
+        <v>29</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM14" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP14" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR14" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BT14" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BW14" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BY14" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BZ14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="CA14" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,189 +4145,189 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="G15" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.08</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.52</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>2.88</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z15" t="n">
         <v>36</v>
       </c>
-      <c r="Z15" t="n">
-        <v>65</v>
-      </c>
       <c r="AA15" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI15" t="n">
         <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>15</v>
       </c>
-      <c r="AL15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AR15" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="AS15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13.5</v>
       </c>
       <c r="BK15" t="n">
         <v>5.8</v>
@@ -4336,53 +4336,307 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>9</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-15 07:03:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="X16" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>370</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV16" t="n">
         <v>21</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="AW16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN16" t="n">
         <v>6.6</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BO16" t="n">
         <v>3.3</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BP16" t="n">
         <v>13</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BQ16" t="n">
         <v>5.8</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="BR16" t="n">
         <v>26</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="BS16" t="n">
         <v>11</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="BT16" t="n">
         <v>14.5</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="BU16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
         <v>21</v>
       </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>21</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="BZ16" t="n">
         <v>15</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CA16" t="n">
         <v>6.4</v>
       </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>2026-07-15 04:55:19</t>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,7 +884,7 @@
         <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="n">
         <v>1.81</v>
@@ -1120,22 +1120,22 @@
         <v>4.4</v>
       </c>
       <c r="I3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.8</v>
       </c>
-      <c r="J3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
@@ -1147,7 +1147,7 @@
         <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
         <v>2.24</v>
@@ -1189,7 +1189,7 @@
         <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1213,25 +1213,25 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
         <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AR3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS3" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS3" t="n">
-        <v>5</v>
-      </c>
       <c r="AT3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>9.800000000000001</v>
@@ -1240,7 +1240,7 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1252,7 +1252,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
         <v>17.5</v>
@@ -1264,77 +1264,77 @@
         <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
         <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="n">
         <v>4.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
         <v>6.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV3" t="n">
         <v>30</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Ecuadorian Serie B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Atletico Rojiblanco</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>San Antonio FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1.44</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.18</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.9</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.15</v>
+        <v>1.37</v>
       </c>
       <c r="G6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO6" t="n">
         <v>3.65</v>
       </c>
-      <c r="H6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="BP6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BN6" t="n">
+      <c r="BZ6" t="n">
         <v>9</v>
       </c>
-      <c r="BO6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>46</v>
-      </c>
       <c r="CA6" t="n">
-        <v>1.71</v>
+        <v>4.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>16.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>46</v>
       </c>
-      <c r="AT7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA7" t="n">
-        <v>11.5</v>
+        <v>1.71</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -2372,97 +2372,97 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>18.5</v>
@@ -2471,147 +2471,147 @@
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG8" t="n">
         <v>30</v>
       </c>
-      <c r="AK8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="BH8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX8" t="n">
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>12</v>
       </c>
-      <c r="AY8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS8" t="n">
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
         <v>11</v>
       </c>
-      <c r="BT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,189 +2621,189 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
         <v>2.12</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.33</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.27</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z9" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB9" t="n">
         <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="n">
         <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB9" t="n">
         <v>23</v>
       </c>
-      <c r="AL9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK9" t="n">
         <v>6.2</v>
@@ -2812,60 +2812,60 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS9" t="n">
         <v>11</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW9" t="n">
         <v>11.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
         <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA9" t="n">
         <v>10.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
         <v>15</v>
       </c>
-      <c r="J10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X10" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AW10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.06</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="U11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>330</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI11" t="n">
         <v>3.6</v>
       </c>
-      <c r="I11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X11" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BJ11" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="CA11" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US MLS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,216 +3383,216 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>CF Montreal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Toronto FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.89</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.79</v>
-      </c>
       <c r="X12" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF12" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
         <v>30</v>
       </c>
       <c r="AK12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC12" t="n">
+      <c r="BK12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN12" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD12" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5</v>
-      </c>
       <c r="BO12" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BR12" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BT12" t="n">
         <v>7.4</v>
@@ -3601,33 +3601,33 @@
         <v>6</v>
       </c>
       <c r="BV12" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BX12" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BZ12" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="G13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.05</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.9</v>
-      </c>
       <c r="K13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S13" t="n">
         <v>4.1</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI13" t="n">
         <v>2.52</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI13" t="n">
+      <c r="BJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR13" t="n">
         <v>36</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL13" t="n">
+      <c r="BS13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV13" t="n">
         <v>38</v>
       </c>
-      <c r="AM13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BW13" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="CA13" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>St Louis City SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>2.88</v>
       </c>
       <c r="G14" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>2.46</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="U14" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.68</v>
       </c>
       <c r="W14" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="n">
         <v>38</v>
       </c>
-      <c r="Y14" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AM14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="BA14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK14" t="n">
+      <c r="BH14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>14</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="BR14" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX14" t="n">
         <v>25</v>
       </c>
-      <c r="AM14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="BY14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="CA14" t="n">
         <v>11</v>
       </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>29</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>100</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>10</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>US MLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>St Louis City SC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.94</v>
       </c>
       <c r="S15" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>3.05</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Y15" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="Z15" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AA15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>19.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AM15" t="n">
         <v>90</v>
       </c>
       <c r="AN15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AU15" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.7</v>
+        <v>48</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.7</v>
+        <v>29</v>
       </c>
       <c r="BB15" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="BF15" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.6</v>
+        <v>29</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM15" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BS15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BT15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>20</v>
-      </c>
       <c r="CA15" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,189 +4399,189 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="G16" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW16" t="n">
         <v>5.7</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="AX16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI16" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X16" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>370</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>350</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>28</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
         <v>5.8</v>
@@ -4590,53 +4590,307 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>9</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X17" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>710</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>340</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>21</v>
       </c>
-      <c r="BN16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO16" t="n">
+      <c r="AR17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO17" t="n">
         <v>3.3</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BP17" t="n">
         <v>13</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BQ17" t="n">
         <v>5.8</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="BR17" t="n">
         <v>26</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="BS17" t="n">
         <v>11</v>
       </c>
-      <c r="BT16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BU16" t="n">
+      <c r="BT17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU17" t="n">
         <v>6.2</v>
       </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
         <v>21</v>
       </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
         <v>21</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="BZ17" t="n">
         <v>15</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CA17" t="n">
         <v>6.4</v>
       </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-07-15 07:03:56</t>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>2.4</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -884,19 +884,19 @@
         <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         <v>1.7</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
         <v>1.58</v>
@@ -1222,7 +1222,7 @@
         <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AR3" t="n">
         <v>4.8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1670,7 +1670,7 @@
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1882,13 +1882,13 @@
         <v>7.2</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.19</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
@@ -1915,13 +1915,13 @@
         <v>1.96</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
         <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
         <v>3.1</v>
@@ -1933,88 +1933,88 @@
         <v>46</v>
       </c>
       <c r="Z6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
         <v>16.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.5</v>
+        <v>1.35</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.8</v>
+        <v>1.35</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>1.35</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>1.35</v>
       </c>
       <c r="AX6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>1.33</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -2026,13 +2026,13 @@
         <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>1.35</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.5</v>
+        <v>1.33</v>
       </c>
       <c r="BH6" t="n">
         <v>5.7</v>
@@ -2044,7 +2044,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,13 +2056,13 @@
         <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP6" t="n">
         <v>8.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
         <v>18</v>
@@ -2074,7 +2074,7 @@
         <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,11 @@
         <v>9</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.65</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I7" t="n">
         <v>2.56</v>
@@ -2142,7 +2142,7 @@
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2175,7 +2175,7 @@
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W7" t="n">
         <v>1.38</v>
@@ -2196,7 +2196,7 @@
         <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
@@ -2244,7 +2244,7 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
         <v>19.5</v>
@@ -2268,22 +2268,22 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG7" t="n">
         <v>16.5</v>
@@ -2310,7 +2310,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
         <v>40</v>
@@ -2328,7 +2328,7 @@
         <v>7.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV7" t="n">
         <v>26</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G8" t="n">
         <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
         <v>3.2</v>
@@ -2396,7 +2396,7 @@
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.45</v>
@@ -2423,7 +2423,7 @@
         <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
         <v>2.1</v>
@@ -2432,7 +2432,7 @@
         <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>12.5</v>
@@ -2459,10 +2459,10 @@
         <v>44</v>
       </c>
       <c r="AF8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>18.5</v>
@@ -2474,7 +2474,7 @@
         <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>50</v>
@@ -2525,7 +2525,7 @@
         <v>44</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
         <v>24</v>
@@ -2540,7 +2540,7 @@
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="n">
         <v>3.25</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2668,7 +2668,7 @@
         <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
@@ -2677,7 +2677,7 @@
         <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U9" t="n">
         <v>2.24</v>
@@ -2686,7 +2686,7 @@
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
@@ -2737,7 +2737,7 @@
         <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>46</v>
@@ -2770,19 +2770,19 @@
         <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BB9" t="n">
         <v>23</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD9" t="n">
         <v>30</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
         <v>2.12</v>
@@ -2901,10 +2901,10 @@
         <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2919,7 +2919,7 @@
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
         <v>1.98</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -3146,16 +3146,16 @@
         <v>1.26</v>
       </c>
       <c r="G11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="H11" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
         <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K11" t="n">
         <v>7.2</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.56</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
         <v>2.06</v>
@@ -3194,7 +3194,7 @@
         <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -3224,7 +3224,7 @@
         <v>9.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>36</v>
@@ -3263,7 +3263,7 @@
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
         <v>1.03</v>
@@ -3275,10 +3275,10 @@
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>1.03</v>
@@ -3287,7 +3287,7 @@
         <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BC11" t="n">
         <v>1.03</v>
@@ -3299,7 +3299,7 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BG11" t="n">
         <v>1.01</v>
@@ -3341,7 +3341,7 @@
         <v>17</v>
       </c>
       <c r="BT11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BU11" t="n">
         <v>11.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -3397,34 +3397,34 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
         <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.31</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
         <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
         <v>2.4</v>
@@ -3436,97 +3436,97 @@
         <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
         <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF12" t="n">
         <v>15</v>
       </c>
-      <c r="AC12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP12" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="AQ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>11</v>
-      </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.7</v>
+        <v>28</v>
       </c>
       <c r="AX12" t="n">
         <v>13</v>
@@ -3535,31 +3535,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.7</v>
+        <v>29</v>
       </c>
       <c r="BB12" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
         <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.9</v>
+        <v>46</v>
       </c>
       <c r="BF12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI12" t="n">
         <v>3.3</v>
@@ -3568,10 +3568,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
         <v>21</v>
@@ -3592,19 +3592,19 @@
         <v>24</v>
       </c>
       <c r="BS12" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BX12" t="n">
         <v>34</v>
@@ -3613,14 +3613,14 @@
         <v>22</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -3726,7 +3726,7 @@
         <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>15</v>
@@ -3765,7 +3765,7 @@
         <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS13" t="n">
         <v>6</v>
@@ -3792,16 +3792,16 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="BE13" t="n">
         <v>6.2</v>
@@ -3810,7 +3810,7 @@
         <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="n">
         <v>3.1</v>
@@ -3822,7 +3822,7 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,7 +3834,7 @@
         <v>5</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP13" t="n">
         <v>17.5</v>
@@ -3852,7 +3852,7 @@
         <v>7.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV13" t="n">
         <v>38</v>
@@ -3861,7 +3861,7 @@
         <v>8.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
         <v>9.199999999999999</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -3911,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J14" t="n">
         <v>3.95</v>
@@ -3929,19 +3929,19 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
         <v>1.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
         <v>2.44</v>
@@ -3950,7 +3950,7 @@
         <v>1.52</v>
       </c>
       <c r="U14" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V14" t="n">
         <v>1.68</v>
@@ -3959,73 +3959,73 @@
         <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
         <v>15.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ14" t="n">
         <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AN14" t="n">
         <v>17.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="AQ14" t="n">
         <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU14" t="n">
         <v>8.4</v>
@@ -4037,34 +4037,34 @@
         <v>19</v>
       </c>
       <c r="AX14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.6</v>
+        <v>26</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.7</v>
+        <v>28</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH14" t="n">
         <v>4.6</v>
@@ -4106,7 +4106,7 @@
         <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV14" t="n">
         <v>17</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G15" t="n">
         <v>1.48</v>
@@ -4174,7 +4174,7 @@
         <v>5.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.23</v>
@@ -4189,16 +4189,16 @@
         <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R15" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T15" t="n">
         <v>1.6</v>
@@ -4213,13 +4213,13 @@
         <v>3.05</v>
       </c>
       <c r="X15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z15" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
@@ -4231,13 +4231,13 @@
         <v>14</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
@@ -4246,31 +4246,31 @@
         <v>19.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
         <v>15</v>
       </c>
       <c r="AK15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM15" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AR15" t="n">
         <v>46</v>
@@ -4279,13 +4279,13 @@
         <v>46</v>
       </c>
       <c r="AT15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>48</v>
@@ -4294,25 +4294,25 @@
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BB15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF15" t="n">
         <v>4.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4446,25 +4446,25 @@
         <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4527,7 +4527,7 @@
         <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
         <v>5.9</v>
@@ -4566,7 +4566,7 @@
         <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4596,7 +4596,7 @@
         <v>4.9</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP16" t="n">
         <v>13.5</v>
@@ -4608,35 +4608,35 @@
         <v>25</v>
       </c>
       <c r="BS16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT16" t="n">
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
       </c>
       <c r="BW16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX16" t="n">
         <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA16" t="n">
         <v>9</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
         <v>5.3</v>
@@ -4805,7 +4805,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>28</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1282,16 +1282,16 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO3" t="n">
         <v>3.85</v>
@@ -1300,25 +1300,25 @@
         <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR3" t="n">
         <v>19.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
         <v>30</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
@@ -1330,11 +1330,11 @@
         <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1643,16 +1643,16 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1882,13 +1882,13 @@
         <v>7.2</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.19</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
@@ -1912,16 +1912,16 @@
         <v>1.84</v>
       </c>
       <c r="S6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
         <v>3.1</v>
@@ -1933,64 +1933,64 @@
         <v>46</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
         <v>16.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM6" t="n">
         <v>85</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.31</v>
+        <v>4.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.31</v>
+        <v>4.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.35</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -1999,22 +1999,22 @@
         <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.35</v>
+        <v>4.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.35</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -2026,13 +2026,13 @@
         <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="BH6" t="n">
         <v>5.7</v>
@@ -2044,7 +2044,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,13 +2056,13 @@
         <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BP6" t="n">
         <v>8.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR6" t="n">
         <v>18</v>
@@ -2074,7 +2074,7 @@
         <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,11 @@
         <v>9</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
@@ -2172,7 +2172,7 @@
         <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
         <v>1.64</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
         <v>1.45</v>
@@ -2408,31 +2408,31 @@
         <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
         <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
         <v>12.5</v>
@@ -2441,22 +2441,22 @@
         <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="n">
         <v>16</v>
@@ -2471,22 +2471,22 @@
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
         <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP8" t="n">
         <v>11</v>
@@ -2501,7 +2501,7 @@
         <v>46</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2513,7 +2513,7 @@
         <v>32</v>
       </c>
       <c r="AX8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
@@ -2525,7 +2525,7 @@
         <v>44</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
         <v>24</v>
@@ -2534,77 +2534,77 @@
         <v>38</v>
       </c>
       <c r="BE8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="BH8" t="n">
         <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
         <v>4.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA8" t="n">
         <v>10</v>
       </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>11</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.85</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.4</v>
@@ -2662,31 +2662,31 @@
         <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U9" t="n">
         <v>2.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
@@ -2737,7 +2737,7 @@
         <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO9" t="n">
         <v>46</v>
@@ -2782,7 +2782,7 @@
         <v>23</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>30</v>
@@ -2800,65 +2800,65 @@
         <v>3.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP9" t="n">
         <v>15.5</v>
       </c>
-      <c r="BN9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>15</v>
-      </c>
       <c r="BQ9" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BR9" t="n">
         <v>28</v>
       </c>
       <c r="BS9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
         <v>7.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>30</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
         <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ9" t="n">
         <v>24</v>
       </c>
       <c r="CA9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
@@ -2907,10 +2907,10 @@
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
         <v>3.7</v>
@@ -2928,7 +2928,7 @@
         <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
         <v>1.8</v>
@@ -2937,31 +2937,31 @@
         <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>65</v>
@@ -2970,10 +2970,10 @@
         <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>75</v>
@@ -2982,10 +2982,10 @@
         <v>26</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
@@ -2997,16 +2997,16 @@
         <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3015,76 +3015,76 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
         <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
         <v>7.4</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.26</v>
       </c>
       <c r="G11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -3179,7 +3179,7 @@
         <v>1.57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
         <v>2.4</v>
@@ -3188,13 +3188,13 @@
         <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
         <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -3215,43 +3215,43 @@
         <v>17</v>
       </c>
       <c r="AD11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AE11" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
         <v>11.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.03</v>
@@ -3266,7 +3266,7 @@
         <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AV11" t="n">
         <v>1.03</v>
@@ -3290,7 +3290,7 @@
         <v>8.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
         <v>1.03</v>
@@ -3299,10 +3299,10 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>220</v>
       </c>
       <c r="BH11" t="n">
         <v>4.7</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
@@ -3421,7 +3421,7 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.22</v>
@@ -3430,13 +3430,13 @@
         <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
         <v>1.61</v>
@@ -3445,16 +3445,16 @@
         <v>2.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
         <v>30</v>
@@ -3463,22 +3463,22 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>16.5</v>
@@ -3487,13 +3487,13 @@
         <v>44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
         <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
         <v>70</v>
@@ -3514,7 +3514,7 @@
         <v>18.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AT12" t="n">
         <v>11.5</v>
@@ -3526,7 +3526,7 @@
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
         <v>13</v>
@@ -3538,7 +3538,7 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
@@ -3550,13 +3550,13 @@
         <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BF12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH12" t="n">
         <v>4.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
         <v>3.05</v>
@@ -3669,49 +3669,49 @@
         <v>3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
         <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X13" t="n">
         <v>12.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
         <v>110</v>
@@ -3720,10 +3720,10 @@
         <v>8.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
         <v>65</v>
@@ -3750,7 +3750,7 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
         <v>26</v>
@@ -3765,10 +3765,10 @@
         <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
         <v>6.8</v>
@@ -3780,7 +3780,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3792,25 +3792,25 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD13" t="n">
         <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
         <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>3.1</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
@@ -3837,7 +3837,7 @@
         <v>3.85</v>
       </c>
       <c r="BP13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ13" t="n">
         <v>6.8</v>
@@ -3846,13 +3846,13 @@
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT13" t="n">
         <v>7.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV13" t="n">
         <v>38</v>
@@ -3870,11 +3870,11 @@
         <v>36</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -3908,16 +3908,16 @@
         <v>2.88</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H14" t="n">
         <v>2.38</v>
       </c>
       <c r="I14" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -3947,10 +3947,10 @@
         <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V14" t="n">
         <v>1.68</v>
@@ -3962,13 +3962,13 @@
         <v>28</v>
       </c>
       <c r="Y14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z14" t="n">
         <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="n">
         <v>19</v>
@@ -3977,28 +3977,28 @@
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
         <v>24</v>
       </c>
       <c r="AF14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
         <v>34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL14" t="n">
         <v>36</v>
@@ -4019,7 +4019,7 @@
         <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
         <v>21</v>
@@ -4028,7 +4028,7 @@
         <v>15.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
@@ -4037,7 +4037,7 @@
         <v>19</v>
       </c>
       <c r="AX14" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
@@ -4046,7 +4046,7 @@
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB14" t="n">
         <v>26</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -4165,10 +4165,10 @@
         <v>1.48</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
         <v>5.4</v>
@@ -4204,13 +4204,13 @@
         <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X15" t="n">
         <v>38</v>
@@ -4321,10 +4321,10 @@
         <v>29</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.800000000000001</v>
@@ -4333,7 +4333,7 @@
         <v>6.8</v>
       </c>
       <c r="BL15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BM15" t="n">
         <v>21</v>
@@ -4342,7 +4342,7 @@
         <v>4.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP15" t="n">
         <v>9</v>
@@ -4351,13 +4351,13 @@
         <v>6.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS15" t="n">
         <v>12</v>
       </c>
       <c r="BT15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU15" t="n">
         <v>7.4</v>
@@ -4369,20 +4369,20 @@
         <v>21</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY15" t="n">
         <v>21</v>
       </c>
       <c r="BZ15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CA15" t="n">
         <v>7.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.94</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -4428,10 +4428,10 @@
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4458,13 +4458,13 @@
         <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4473,10 +4473,10 @@
         <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB16" t="n">
         <v>12.5</v>
@@ -4497,7 +4497,7 @@
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
@@ -4509,16 +4509,16 @@
         <v>23</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
         <v>12.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP16" t="n">
         <v>16</v>
@@ -4527,22 +4527,22 @@
         <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -4554,25 +4554,25 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH16" t="n">
         <v>3.8</v>
@@ -4614,7 +4614,7 @@
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
         <v>5.3</v>
@@ -4694,7 +4694,7 @@
         <v>7.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
         <v>3.15</v>
@@ -4709,10 +4709,10 @@
         <v>2.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
@@ -4727,7 +4727,7 @@
         <v>65</v>
       </c>
       <c r="Z17" t="n">
-        <v>710</v>
+        <v>670</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4745,16 +4745,16 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
@@ -4772,22 +4772,22 @@
         <v>4.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AP17" t="n">
         <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AR17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS17" t="n">
         <v>44</v>
       </c>
       <c r="AT17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
         <v>11.5</v>
@@ -4805,7 +4805,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
         <v>28</v>
@@ -4823,7 +4823,7 @@
         <v>32</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
         <v>28</v>
@@ -4856,7 +4856,7 @@
         <v>13</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR17" t="n">
         <v>26</v>
@@ -4883,14 +4883,14 @@
         <v>21</v>
       </c>
       <c r="BZ17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA17" t="n">
         <v>6.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -905,7 +905,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
         <v>1.12</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.21</v>
@@ -1135,28 +1135,28 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
         <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S3" t="n">
         <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V3" t="n">
         <v>1.21</v>
@@ -1168,7 +1168,7 @@
         <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
         <v>48</v>
@@ -1180,7 +1180,7 @@
         <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
         <v>24</v>
@@ -1207,28 +1207,28 @@
         <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
         <v>21</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1240,7 +1240,7 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1252,7 +1252,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB3" t="n">
         <v>17.5</v>
@@ -1264,13 +1264,13 @@
         <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
         <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="n">
         <v>4.8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>1.29</v>
+        <v>2.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>1.13</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
         <v>2.2</v>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
         <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>1.83</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>7.2</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K6" t="n">
         <v>6.2</v>
@@ -1903,10 +1903,10 @@
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R6" t="n">
         <v>1.84</v>
@@ -1915,7 +1915,7 @@
         <v>1.95</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
         <v>2.28</v>
@@ -1945,13 +1945,13 @@
         <v>16.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
         <v>110</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
         <v>13.5</v>
@@ -1981,7 +1981,7 @@
         <v>80</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
         <v>4.9</v>
@@ -1990,7 +1990,7 @@
         <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -2005,10 +2005,10 @@
         <v>5.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>16</v>
@@ -2029,7 +2029,7 @@
         <v>5.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="BG6" t="n">
         <v>5.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>2.28</v>
       </c>
       <c r="I7" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
@@ -2145,7 +2145,7 @@
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
@@ -2169,13 +2169,13 @@
         <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
         <v>1.38</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
         <v>2.54</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
@@ -2408,16 +2408,16 @@
         <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
         <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
         <v>3.95</v>
@@ -2429,10 +2429,10 @@
         <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X8" t="n">
         <v>12.5</v>
@@ -2441,7 +2441,7 @@
         <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
         <v>60</v>
@@ -2585,7 +2585,7 @@
         <v>4.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
         <v>9.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
@@ -2668,25 +2668,25 @@
         <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
         <v>2.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
@@ -2698,7 +2698,7 @@
         <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="n">
         <v>11</v>
@@ -2761,7 +2761,7 @@
         <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW9" t="n">
         <v>38</v>
@@ -2773,13 +2773,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC9" t="n">
         <v>19</v>
@@ -2800,28 +2800,28 @@
         <v>3.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ9" t="n">
         <v>7.8</v>
@@ -2830,35 +2830,35 @@
         <v>28</v>
       </c>
       <c r="BS9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT9" t="n">
         <v>7.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
         <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>24</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2901,13 +2901,13 @@
         <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2919,7 +2919,7 @@
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
         <v>1.98</v>
@@ -2949,7 +2949,7 @@
         <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
         <v>110</v>
@@ -2961,7 +2961,7 @@
         <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
         <v>65</v>
@@ -2973,7 +2973,7 @@
         <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>75</v>
@@ -2991,7 +2991,7 @@
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>70</v>
@@ -3003,10 +3003,10 @@
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
         <v>9.6</v>
@@ -3027,28 +3027,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD10" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
         <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH10" t="n">
         <v>3.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
         <v>2.12</v>
@@ -3406,7 +3406,7 @@
         <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -3427,7 +3427,7 @@
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q12" t="n">
         <v>1.67</v>
@@ -3439,7 +3439,7 @@
         <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
         <v>2.52</v>
@@ -3466,7 +3466,7 @@
         <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>16</v>
@@ -3511,7 +3511,7 @@
         <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS12" t="n">
         <v>32</v>
@@ -3553,10 +3553,10 @@
         <v>32</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH12" t="n">
         <v>4.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
@@ -3666,7 +3666,7 @@
         <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.47</v>
@@ -3702,7 +3702,7 @@
         <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X13" t="n">
         <v>12.5</v>
@@ -3741,7 +3741,7 @@
         <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK13" t="n">
         <v>32</v>
@@ -3765,10 +3765,10 @@
         <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>6.8</v>
@@ -3780,7 +3780,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3792,25 +3792,25 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD13" t="n">
         <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
         <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
         <v>3.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>2.88</v>
       </c>
       <c r="G14" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>2.38</v>
@@ -3929,7 +3929,7 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
@@ -3944,7 +3944,7 @@
         <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T14" t="n">
         <v>1.53</v>
@@ -3959,7 +3959,7 @@
         <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y14" t="n">
         <v>17</v>
@@ -3977,7 +3977,7 @@
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>24</v>
@@ -4004,7 +4004,7 @@
         <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN14" t="n">
         <v>17.5</v>
@@ -4013,16 +4013,16 @@
         <v>13</v>
       </c>
       <c r="AP14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ14" t="n">
         <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT14" t="n">
         <v>15.5</v>
@@ -4046,13 +4046,13 @@
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB14" t="n">
         <v>26</v>
       </c>
       <c r="BC14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD14" t="n">
         <v>20</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -4165,10 +4165,10 @@
         <v>1.48</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
         <v>5.4</v>
@@ -4204,19 +4204,19 @@
         <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X15" t="n">
         <v>38</v>
       </c>
       <c r="Y15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z15" t="n">
         <v>75</v>
@@ -4237,13 +4237,13 @@
         <v>80</v>
       </c>
       <c r="AF15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
         <v>65</v>
@@ -4261,7 +4261,7 @@
         <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4315,7 +4315,7 @@
         <v>55</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
         <v>29</v>
@@ -4324,7 +4324,7 @@
         <v>5.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.800000000000001</v>
@@ -4333,7 +4333,7 @@
         <v>6.8</v>
       </c>
       <c r="BL15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BM15" t="n">
         <v>21</v>
@@ -4342,7 +4342,7 @@
         <v>4.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP15" t="n">
         <v>9</v>
@@ -4351,7 +4351,7 @@
         <v>6.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS15" t="n">
         <v>12</v>
@@ -4375,14 +4375,14 @@
         <v>21</v>
       </c>
       <c r="BZ15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA15" t="n">
         <v>7.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.3</v>
@@ -4443,10 +4443,10 @@
         <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
@@ -4461,7 +4461,7 @@
         <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
@@ -4482,7 +4482,7 @@
         <v>12.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
         <v>17.5</v>
@@ -4491,7 +4491,7 @@
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
@@ -4503,7 +4503,7 @@
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>23</v>
@@ -4530,7 +4530,7 @@
         <v>5.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
@@ -4542,7 +4542,7 @@
         <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -4554,13 +4554,13 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H17" t="n">
         <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -4691,7 +4691,7 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.14</v>
@@ -4700,7 +4700,7 @@
         <v>3.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R17" t="n">
         <v>1.86</v>
@@ -4718,16 +4718,16 @@
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X17" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Y17" t="n">
         <v>65</v>
       </c>
       <c r="Z17" t="n">
-        <v>670</v>
+        <v>750</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4736,7 +4736,7 @@
         <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD17" t="n">
         <v>36</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
@@ -4754,7 +4754,7 @@
         <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
@@ -4772,16 +4772,16 @@
         <v>4.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AP17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ17" t="n">
         <v>29</v>
       </c>
       <c r="AR17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
         <v>44</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -890,13 +890,13 @@
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
         <v>4.4</v>
@@ -1129,7 +1129,7 @@
         <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1144,31 +1144,31 @@
         <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.22</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="n">
         <v>48</v>
@@ -1180,10 +1180,10 @@
         <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>60</v>
@@ -1192,7 +1192,7 @@
         <v>17.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>19.5</v>
@@ -1201,10 +1201,10 @@
         <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
         <v>26</v>
@@ -1213,22 +1213,22 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
         <v>36</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ3" t="n">
         <v>21</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1240,7 +1240,7 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1252,7 +1252,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
         <v>17.5</v>
@@ -1264,34 +1264,34 @@
         <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF3" t="n">
         <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM3" t="n">
         <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
         <v>3.85</v>
@@ -1303,10 +1303,10 @@
         <v>6.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
@@ -1321,20 +1321,20 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY3" t="n">
         <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1377,10 +1377,10 @@
         <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.22</v>
@@ -1404,13 +1404,13 @@
         <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
         <v>1.46</v>
       </c>
       <c r="U4" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V4" t="n">
         <v>1.4</v>
@@ -1419,7 +1419,7 @@
         <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
         <v>23</v>
@@ -1428,7 +1428,7 @@
         <v>30</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
         <v>18</v>
@@ -1464,7 +1464,7 @@
         <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN4" t="n">
         <v>10.5</v>
@@ -1473,58 +1473,58 @@
         <v>18.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.4</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BD4" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
         <v>4.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH4" t="n">
         <v>5.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.83</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -1963,7 +1963,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK6" t="n">
         <v>16</v>
@@ -1972,7 +1972,7 @@
         <v>30</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
         <v>4.6</v>
@@ -1981,16 +1981,16 @@
         <v>80</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ6" t="n">
         <v>4.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -1999,10 +1999,10 @@
         <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX6" t="n">
         <v>9.4</v>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -2026,19 +2026,19 @@
         <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="n">
         <v>5.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2062,7 +2062,7 @@
         <v>8.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR6" t="n">
         <v>18</v>
@@ -2074,7 +2074,7 @@
         <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.15</v>
       </c>
       <c r="G7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H7" t="n">
         <v>2.28</v>
@@ -2157,7 +2157,7 @@
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
         <v>2.02</v>
@@ -2166,7 +2166,7 @@
         <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
         <v>1.79</v>
@@ -2223,7 +2223,7 @@
         <v>50</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>120</v>
@@ -2244,7 +2244,7 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
         <v>19.5</v>
@@ -2268,22 +2268,22 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD7" t="n">
         <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG7" t="n">
         <v>16.5</v>
@@ -2292,65 +2292,65 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>1.58</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>46</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.71</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
         <v>3.25</v>
@@ -2423,7 +2423,7 @@
         <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
         <v>2.08</v>
@@ -2438,7 +2438,7 @@
         <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
         <v>23</v>
@@ -2456,7 +2456,7 @@
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
         <v>16</v>
@@ -2465,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>55</v>
@@ -2525,7 +2525,7 @@
         <v>44</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BC8" t="n">
         <v>24</v>
@@ -2534,7 +2534,7 @@
         <v>38</v>
       </c>
       <c r="BE8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
@@ -2546,7 +2546,7 @@
         <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.800000000000001</v>
@@ -2558,53 +2558,53 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>32</v>
       </c>
       <c r="CA8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2656,10 +2656,10 @@
         <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
@@ -2689,7 +2689,7 @@
         <v>1.91</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
         <v>19</v>
@@ -2704,7 +2704,7 @@
         <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
         <v>16</v>
@@ -2737,13 +2737,13 @@
         <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
         <v>46</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>14.5</v>
@@ -2752,7 +2752,7 @@
         <v>25</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
         <v>9.4</v>
@@ -2788,7 +2788,7 @@
         <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
         <v>12.5</v>
@@ -2800,19 +2800,19 @@
         <v>3.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN9" t="n">
         <v>4.9</v>
@@ -2821,7 +2821,7 @@
         <v>3.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>7.8</v>
@@ -2836,7 +2836,7 @@
         <v>7.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
         <v>32</v>
@@ -2848,17 +2848,17 @@
         <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9" t="n">
         <v>24</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
         <v>4.2</v>
@@ -2901,10 +2901,10 @@
         <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.34</v>
@@ -2940,13 +2940,13 @@
         <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z10" t="n">
         <v>38</v>
@@ -2955,7 +2955,7 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
         <v>9.4</v>
@@ -3003,10 +3003,10 @@
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX10" t="n">
         <v>9.6</v>
@@ -3027,28 +3027,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD10" t="n">
+      <c r="BE10" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
         <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="n">
         <v>3.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
         <v>1.67</v>
@@ -3439,13 +3439,13 @@
         <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
         <v>2.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
         <v>1.89</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
         <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
@@ -3741,7 +3741,7 @@
         <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
         <v>32</v>
@@ -3765,10 +3765,10 @@
         <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
         <v>6.8</v>
@@ -3792,7 +3792,7 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
@@ -3810,7 +3810,7 @@
         <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>3.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I14" t="n">
         <v>2.46</v>
@@ -3929,16 +3929,16 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R14" t="n">
         <v>1.65</v>
@@ -3950,7 +3950,7 @@
         <v>1.53</v>
       </c>
       <c r="U14" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V14" t="n">
         <v>1.68</v>
@@ -3959,10 +3959,10 @@
         <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z14" t="n">
         <v>20</v>
@@ -3971,13 +3971,13 @@
         <v>36</v>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC14" t="n">
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
         <v>24</v>
@@ -3995,7 +3995,7 @@
         <v>34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK14" t="n">
         <v>29</v>
@@ -4004,7 +4004,7 @@
         <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN14" t="n">
         <v>17.5</v>
@@ -4091,7 +4091,7 @@
         <v>4.9</v>
       </c>
       <c r="BP14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ14" t="n">
         <v>14</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H15" t="n">
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>5.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.23</v>
@@ -4186,7 +4186,7 @@
         <v>7.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P15" t="n">
         <v>3.25</v>
@@ -4195,7 +4195,7 @@
         <v>1.42</v>
       </c>
       <c r="R15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S15" t="n">
         <v>2.04</v>
@@ -4210,13 +4210,13 @@
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
         <v>38</v>
       </c>
       <c r="Y15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z15" t="n">
         <v>75</v>
@@ -4228,10 +4228,10 @@
         <v>15</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
         <v>80</v>
@@ -4252,7 +4252,7 @@
         <v>15</v>
       </c>
       <c r="AK15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL15" t="n">
         <v>23</v>
@@ -4285,7 +4285,7 @@
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
         <v>48</v>
@@ -4300,7 +4300,7 @@
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="BB15" t="n">
         <v>13.5</v>
@@ -4315,10 +4315,10 @@
         <v>55</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BH15" t="n">
         <v>5.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.94</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -4449,7 +4449,7 @@
         <v>1.77</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
         <v>2.96</v>
@@ -4461,7 +4461,7 @@
         <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
@@ -4470,7 +4470,7 @@
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
         <v>38</v>
@@ -4527,10 +4527,10 @@
         <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
@@ -4542,7 +4542,7 @@
         <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -4554,7 +4554,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -4566,13 +4566,13 @@
         <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH16" t="n">
         <v>3.8</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H17" t="n">
         <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
         <v>5.2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -4691,7 +4691,7 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.14</v>
@@ -4700,7 +4700,7 @@
         <v>3.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R17" t="n">
         <v>1.86</v>
@@ -4718,16 +4718,16 @@
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X17" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Y17" t="n">
         <v>65</v>
       </c>
       <c r="Z17" t="n">
-        <v>750</v>
+        <v>860</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4736,7 +4736,7 @@
         <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>36</v>
@@ -4754,7 +4754,7 @@
         <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
@@ -4772,13 +4772,13 @@
         <v>4.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AP17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>2.98</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
         <v>1.48</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.69</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -926,7 +926,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -947,7 +947,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
         <v>1000</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1111,136 +1111,136 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
         <v>110</v>
       </c>
       <c r="AB3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>44</v>
       </c>
       <c r="AJ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL3" t="n">
         <v>24</v>
       </c>
-      <c r="AK3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>26</v>
-      </c>
       <c r="AM3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO3" t="n">
         <v>36</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.3</v>
+        <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1249,46 +1249,46 @@
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
         <v>17.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>5</v>
@@ -1297,44 +1297,44 @@
         <v>3.85</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV3" t="n">
         <v>30</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1377,19 +1377,19 @@
         <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.22</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
@@ -1419,16 +1419,16 @@
         <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Y4" t="n">
         <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
         <v>18</v>
@@ -1440,19 +1440,19 @@
         <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
         <v>32</v>
@@ -1461,10 +1461,10 @@
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM4" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AN4" t="n">
         <v>10.5</v>
@@ -1473,37 +1473,37 @@
         <v>18.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV4" t="n">
         <v>5.1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.9</v>
       </c>
       <c r="AW4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA4" t="n">
         <v>9.199999999999999</v>
@@ -1512,19 +1512,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH4" t="n">
         <v>5.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
         <v>2.2</v>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1688,7 +1688,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1727,58 +1727,58 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H6" t="n">
         <v>7.2</v>
       </c>
       <c r="I6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K6" t="n">
         <v>6.2</v>
@@ -1894,7 +1894,7 @@
         <v>1.19</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
         <v>7</v>
@@ -1909,10 +1909,10 @@
         <v>1.39</v>
       </c>
       <c r="R6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T6" t="n">
         <v>1.63</v>
@@ -1924,73 +1924,73 @@
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X6" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="Y6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z6" t="n">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="AA6" t="n">
         <v>240</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
         <v>34</v>
       </c>
       <c r="AE6" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AO6" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -1999,10 +1999,10 @@
         <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
         <v>9.4</v>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -2023,28 +2023,28 @@
         <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
         <v>3.65</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="n">
         <v>5.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2062,7 +2062,7 @@
         <v>8.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR6" t="n">
         <v>18</v>
@@ -2074,7 +2074,7 @@
         <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
         <v>3.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.17</v>
@@ -2163,7 +2163,7 @@
         <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
         <v>3.7</v>
@@ -2172,7 +2172,7 @@
         <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
         <v>1.65</v>
@@ -2181,19 +2181,19 @@
         <v>1.38</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -2202,37 +2202,37 @@
         <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
         <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
@@ -2244,46 +2244,46 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY7" t="n">
         <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG7" t="n">
         <v>16.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.45</v>
@@ -2417,22 +2417,22 @@
         <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>12.5</v>
@@ -2441,7 +2441,7 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
         <v>60</v>
@@ -2459,10 +2459,10 @@
         <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>18</v>
@@ -2471,10 +2471,10 @@
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
         <v>44</v>
@@ -2483,7 +2483,7 @@
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>40</v>
@@ -2495,10 +2495,10 @@
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
         <v>9</v>
@@ -2507,10 +2507,10 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -2528,19 +2528,19 @@
         <v>30</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
         <v>38</v>
       </c>
       <c r="BE8" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH8" t="n">
         <v>3.25</v>
@@ -2564,13 +2564,13 @@
         <v>5.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP8" t="n">
         <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2582,7 +2582,7 @@
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
@@ -2659,25 +2659,25 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
         <v>2.24</v>
@@ -2686,13 +2686,13 @@
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z9" t="n">
         <v>29</v>
@@ -2701,10 +2701,10 @@
         <v>80</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>16</v>
@@ -2716,16 +2716,16 @@
         <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AK9" t="n">
         <v>21</v>
@@ -2734,7 +2734,7 @@
         <v>34</v>
       </c>
       <c r="AM9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
         <v>14</v>
@@ -2743,22 +2743,22 @@
         <v>46</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
         <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="AT9" t="n">
         <v>9.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>14.5</v>
@@ -2773,7 +2773,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
         <v>44</v>
@@ -2782,19 +2782,19 @@
         <v>22</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD9" t="n">
         <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BF9" t="n">
         <v>12.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH9" t="n">
         <v>3.5</v>
@@ -2818,7 +2818,7 @@
         <v>4.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
         <v>14.5</v>
@@ -2836,7 +2836,7 @@
         <v>7.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>32</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
         <v>4.2</v>
@@ -2901,19 +2901,19 @@
         <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
@@ -2928,46 +2928,46 @@
         <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
         <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
@@ -2976,10 +2976,10 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
         <v>27</v>
@@ -2991,7 +2991,7 @@
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>70</v>
@@ -3000,13 +3000,13 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3015,40 +3015,40 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB10" t="n">
         <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG10" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.3</v>
       </c>
       <c r="BH10" t="n">
         <v>3.4</v>
@@ -3057,7 +3057,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK10" t="n">
         <v>6</v>
@@ -3066,25 +3066,25 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN10" t="n">
         <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP10" t="n">
         <v>15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
         <v>7.4</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -3152,10 +3152,10 @@
         <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
         <v>7.2</v>
@@ -3170,13 +3170,13 @@
         <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
         <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
         <v>1.55</v>
@@ -3191,10 +3191,10 @@
         <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -3263,7 +3263,7 @@
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -3275,10 +3275,10 @@
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
         <v>1.03</v>
@@ -3356,7 +3356,7 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BZ11" t="n">
         <v>11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -3421,46 +3421,46 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="V12" t="n">
         <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
         <v>13</v>
@@ -3475,10 +3475,10 @@
         <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
         <v>16.5</v>
@@ -3502,13 +3502,13 @@
         <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
         <v>19.5</v>
@@ -3517,7 +3517,7 @@
         <v>32</v>
       </c>
       <c r="AT12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
         <v>8.4</v>
@@ -3526,7 +3526,7 @@
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX12" t="n">
         <v>13</v>
@@ -3544,10 +3544,10 @@
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
         <v>32</v>
@@ -3568,13 +3568,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BN12" t="n">
         <v>5.4</v>
@@ -3583,10 +3583,10 @@
         <v>4.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR12" t="n">
         <v>24</v>
@@ -3598,29 +3598,29 @@
         <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV12" t="n">
         <v>27</v>
       </c>
       <c r="BW12" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BX12" t="n">
         <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BZ12" t="n">
         <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -3654,16 +3654,16 @@
         <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
@@ -3675,22 +3675,22 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O13" t="n">
         <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
         <v>1.9</v>
@@ -3705,112 +3705,112 @@
         <v>1.74</v>
       </c>
       <c r="X13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
         <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC13" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AD13" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
         <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK13" t="n">
         <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX13" t="n">
         <v>11</v>
       </c>
-      <c r="AR13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>36</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH13" t="n">
         <v>3.1</v>
@@ -3828,13 +3828,13 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BP13" t="n">
         <v>18</v>
@@ -3843,13 +3843,13 @@
         <v>6.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU13" t="n">
         <v>5.5</v>
@@ -3867,14 +3867,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H14" t="n">
         <v>2.42</v>
       </c>
       <c r="I14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3935,10 +3935,10 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
         <v>1.65</v>
@@ -3950,25 +3950,25 @@
         <v>1.53</v>
       </c>
       <c r="U14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
         <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
         <v>18</v>
@@ -3980,7 +3980,7 @@
         <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF14" t="n">
         <v>24</v>
@@ -3992,37 +3992,37 @@
         <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ14" t="n">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>13</v>
       </c>
       <c r="AP14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ14" t="n">
         <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AT14" t="n">
         <v>15.5</v>
@@ -4034,10 +4034,10 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
@@ -4046,19 +4046,19 @@
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BB14" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BC14" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BE14" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BF14" t="n">
         <v>15</v>
@@ -4088,19 +4088,19 @@
         <v>6.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP14" t="n">
         <v>20</v>
       </c>
       <c r="BQ14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BR14" t="n">
         <v>27</v>
       </c>
       <c r="BS14" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
@@ -4112,23 +4112,23 @@
         <v>17</v>
       </c>
       <c r="BW14" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX14" t="n">
         <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BZ14" t="n">
         <v>16.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
         <v>5.4</v>
@@ -4189,7 +4189,7 @@
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
         <v>1.42</v>
@@ -4204,7 +4204,7 @@
         <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
@@ -4219,10 +4219,10 @@
         <v>42</v>
       </c>
       <c r="Z15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="n">
         <v>15</v>
@@ -4234,7 +4234,7 @@
         <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="n">
         <v>13</v>
@@ -4243,13 +4243,13 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
         <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK15" t="n">
         <v>14.5</v>
@@ -4261,7 +4261,7 @@
         <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4273,7 +4273,7 @@
         <v>36</v>
       </c>
       <c r="AR15" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AS15" t="n">
         <v>46</v>
@@ -4288,7 +4288,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -4306,7 +4306,7 @@
         <v>13.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>20</v>
@@ -4324,55 +4324,55 @@
         <v>5.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL15" t="n">
         <v>75</v>
       </c>
       <c r="BM15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO15" t="n">
         <v>4.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR15" t="n">
         <v>18</v>
       </c>
       <c r="BS15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BV15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW15" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BX15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BZ15" t="n">
         <v>9.800000000000001</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G16" t="n">
         <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -4449,61 +4449,61 @@
         <v>1.77</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T16" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
         <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK16" t="n">
         <v>23</v>
@@ -4512,67 +4512,67 @@
         <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR16" t="n">
         <v>5.4</v>
       </c>
       <c r="AS16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW16" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AX16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY16" t="n">
         <v>9.6</v>
       </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>5.3</v>
       </c>
       <c r="BB16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH16" t="n">
         <v>3.8</v>
@@ -4581,10 +4581,10 @@
         <v>3.1</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4599,10 +4599,10 @@
         <v>4.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
         <v>25</v>
@@ -4614,7 +4614,7 @@
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G17" t="n">
         <v>1.54</v>
@@ -4679,10 +4679,10 @@
         <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -4694,7 +4694,7 @@
         <v>7.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P17" t="n">
         <v>3.15</v>
@@ -4709,55 +4709,55 @@
         <v>2.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="X17" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="Y17" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Z17" t="n">
-        <v>860</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
         <v>13</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>12.5</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>340</v>
+        <v>240</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK17" t="n">
         <v>14</v>
@@ -4769,13 +4769,13 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO17" t="n">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="AP17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ17" t="n">
         <v>22</v>
@@ -4790,7 +4790,7 @@
         <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>21</v>
@@ -4799,13 +4799,13 @@
         <v>32</v>
       </c>
       <c r="AX17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY17" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
         <v>28</v>
@@ -4814,16 +4814,16 @@
         <v>13.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD17" t="n">
         <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
         <v>28</v>
@@ -4850,7 +4850,7 @@
         <v>6.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP17" t="n">
         <v>13</v>
@@ -4862,13 +4862,13 @@
         <v>26</v>
       </c>
       <c r="BS17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT17" t="n">
         <v>15</v>
       </c>
       <c r="BU17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>14.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -860,7 +860,7 @@
         <v>1.51</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
         <v>2.98</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.48</v>
@@ -896,13 +896,13 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.16</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -1114,91 +1114,91 @@
         <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.6</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="V3" t="n">
         <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
       </c>
       <c r="AE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI3" t="n">
         <v>48</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>44</v>
       </c>
       <c r="AJ3" t="n">
         <v>23</v>
@@ -1207,34 +1207,34 @@
         <v>16</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
         <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>23</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>24</v>
       </c>
       <c r="AR3" t="n">
         <v>38</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV3" t="n">
         <v>17</v>
@@ -1243,7 +1243,7 @@
         <v>40</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
         <v>9.6</v>
@@ -1267,13 +1267,13 @@
         <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
         <v>26</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BI3" t="n">
         <v>3.7</v>
@@ -1282,16 +1282,16 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BO3" t="n">
         <v>3.85</v>
@@ -1300,41 +1300,41 @@
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -1368,55 +1368,55 @@
         <v>2.06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>1.22</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="R4" t="n">
         <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="U4" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
         <v>75</v>
@@ -1428,7 +1428,7 @@
         <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
         <v>18</v>
@@ -1461,10 +1461,10 @@
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>27</v>
+        <v>210</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>10.5</v>
@@ -1515,7 +1515,7 @@
         <v>5.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE4" t="n">
         <v>9.199999999999999</v>
@@ -1527,68 +1527,68 @@
         <v>5.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="BP4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="BR4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q5" t="n">
         <v>1.83</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1688,7 +1688,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1727,55 +1727,55 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU5" t="n">
         <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG5" t="n">
         <v>1.55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>3.15</v>
       </c>
       <c r="X6" t="n">
-        <v>95</v>
+        <v>240</v>
       </c>
       <c r="Y6" t="n">
         <v>48</v>
@@ -1954,7 +1954,7 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
@@ -1981,16 +1981,16 @@
         <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -2002,7 +2002,7 @@
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX6" t="n">
         <v>9.4</v>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -2026,10 +2026,10 @@
         <v>19</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
         <v>10.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
         <v>2.02</v>
@@ -2187,7 +2187,7 @@
         <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
         <v>42</v>
@@ -2196,7 +2196,7 @@
         <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
@@ -2232,7 +2232,7 @@
         <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
@@ -2268,19 +2268,19 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
         <v>7.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G8" t="n">
         <v>2.5</v>
       </c>
       <c r="H8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I8" t="n">
         <v>3.25</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
@@ -2411,25 +2411,25 @@
         <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
         <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
         <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
         <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
         <v>1.66</v>
@@ -2441,7 +2441,7 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
         <v>60</v>
@@ -2459,19 +2459,19 @@
         <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
@@ -2501,7 +2501,7 @@
         <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2534,7 +2534,7 @@
         <v>38</v>
       </c>
       <c r="BE8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF8" t="n">
         <v>21</v>
@@ -2543,7 +2543,7 @@
         <v>34</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI8" t="n">
         <v>2.7</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.3</v>
@@ -2576,35 +2576,35 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ8" t="n">
         <v>32</v>
       </c>
       <c r="CA8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
         <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
@@ -2659,64 +2659,64 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
         <v>80</v>
       </c>
       <c r="AB9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
         <v>16</v>
       </c>
       <c r="AE9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>17.5</v>
@@ -2737,25 +2737,25 @@
         <v>90</v>
       </c>
       <c r="AN9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>14</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
         <v>26</v>
       </c>
       <c r="AS9" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
@@ -2770,7 +2770,7 @@
         <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
@@ -2782,55 +2782,55 @@
         <v>22</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BF9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
         <v>4.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ9" t="n">
         <v>7.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT9" t="n">
         <v>7.2</v>
@@ -2845,20 +2845,20 @@
         <v>11</v>
       </c>
       <c r="BX9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BY9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CA9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
         <v>4.2</v>
@@ -2913,7 +2913,7 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
@@ -2937,10 +2937,10 @@
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
@@ -2958,7 +2958,7 @@
         <v>9.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
         <v>20</v>
@@ -2985,7 +2985,7 @@
         <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
@@ -3027,28 +3027,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
         <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH10" t="n">
         <v>3.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -3152,10 +3152,10 @@
         <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="J11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="K11" t="n">
         <v>7.2</v>
@@ -3167,10 +3167,10 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
         <v>2.36</v>
@@ -3182,7 +3182,7 @@
         <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T11" t="n">
         <v>2.06</v>
@@ -3194,7 +3194,7 @@
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -3308,7 +3308,7 @@
         <v>4.7</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ11" t="n">
         <v>13.5</v>
@@ -3329,7 +3329,7 @@
         <v>3.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BQ11" t="n">
         <v>5.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -3397,64 +3397,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
@@ -3463,7 +3463,7 @@
         <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
         <v>9.199999999999999</v>
@@ -3490,10 +3490,10 @@
         <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM12" t="n">
         <v>70</v>
@@ -3502,13 +3502,13 @@
         <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR12" t="n">
         <v>19.5</v>
@@ -3517,13 +3517,13 @@
         <v>32</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
         <v>23</v>
@@ -3532,7 +3532,7 @@
         <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>14</v>
@@ -3547,19 +3547,19 @@
         <v>16.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BE12" t="n">
         <v>32</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
         <v>21</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI12" t="n">
         <v>3.3</v>
@@ -3568,16 +3568,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL12" t="n">
         <v>85</v>
       </c>
       <c r="BM12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO12" t="n">
         <v>4.5</v>
@@ -3592,7 +3592,7 @@
         <v>24</v>
       </c>
       <c r="BS12" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BT12" t="n">
         <v>7.6</v>
@@ -3616,11 +3616,11 @@
         <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -3669,34 +3669,34 @@
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
         <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
         <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V13" t="n">
         <v>1.3</v>
@@ -3708,25 +3708,25 @@
         <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
         <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>15.5</v>
@@ -3747,7 +3747,7 @@
         <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
@@ -3765,10 +3765,10 @@
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AT13" t="n">
         <v>7</v>
@@ -3780,7 +3780,7 @@
         <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3792,28 +3792,28 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
         <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI13" t="n">
         <v>2.52</v>
@@ -3822,31 +3822,31 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BP13" t="n">
         <v>18</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>7.2</v>
@@ -3855,26 +3855,26 @@
         <v>5.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>36</v>
+      </c>
+      <c r="CA13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ13" t="n">
-        <v>38</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>8.6</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -3911,10 +3911,10 @@
         <v>2.96</v>
       </c>
       <c r="H14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3929,7 +3929,7 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
@@ -3941,19 +3941,19 @@
         <v>1.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
         <v>2.46</v>
       </c>
       <c r="T14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U14" t="n">
         <v>2.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W14" t="n">
         <v>1.51</v>
@@ -3968,7 +3968,7 @@
         <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="n">
         <v>18</v>
@@ -3995,7 +3995,7 @@
         <v>29</v>
       </c>
       <c r="AJ14" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK14" t="n">
         <v>28</v>
@@ -4013,7 +4013,7 @@
         <v>13</v>
       </c>
       <c r="AP14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ14" t="n">
         <v>14</v>
@@ -4028,7 +4028,7 @@
         <v>15.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
@@ -4115,7 +4115,7 @@
         <v>13.5</v>
       </c>
       <c r="BX14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY14" t="n">
         <v>17</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K15" t="n">
         <v>5.5</v>
@@ -4192,7 +4192,7 @@
         <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
         <v>1.91</v>
@@ -4204,10 +4204,10 @@
         <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
         <v>3</v>
@@ -4240,7 +4240,7 @@
         <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>18.5</v>
@@ -4258,10 +4258,10 @@
         <v>23</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4273,7 +4273,7 @@
         <v>36</v>
       </c>
       <c r="AR15" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AS15" t="n">
         <v>46</v>
@@ -4288,7 +4288,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -4300,7 +4300,7 @@
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BB15" t="n">
         <v>13.5</v>
@@ -4315,10 +4315,10 @@
         <v>55</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BH15" t="n">
         <v>5.5</v>
@@ -4339,13 +4339,13 @@
         <v>22</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO15" t="n">
         <v>4.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ15" t="n">
         <v>6.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G16" t="n">
         <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4446,7 +4446,7 @@
         <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
@@ -4461,7 +4461,7 @@
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.98</v>
@@ -4470,7 +4470,7 @@
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z16" t="n">
         <v>36</v>
@@ -4485,13 +4485,13 @@
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
@@ -4500,10 +4500,10 @@
         <v>16.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
         <v>23</v>
@@ -4515,7 +4515,7 @@
         <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO16" t="n">
         <v>48</v>
@@ -4530,7 +4530,7 @@
         <v>5.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB16" t="n">
         <v>20</v>
@@ -4566,7 +4566,7 @@
         <v>5.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
@@ -4581,7 +4581,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
         <v>6.2</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN16" t="n">
         <v>4.9</v>
@@ -4602,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR16" t="n">
         <v>25</v>
@@ -4614,7 +4614,7 @@
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
@@ -4623,20 +4623,20 @@
         <v>11</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ16" t="n">
         <v>19.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
         <v>1.54</v>
@@ -4676,7 +4676,7 @@
         <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
         <v>5.1</v>
@@ -4697,16 +4697,16 @@
         <v>1.15</v>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
         <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T17" t="n">
         <v>1.59</v>
@@ -4718,7 +4718,7 @@
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="X17" t="n">
         <v>38</v>
@@ -4727,7 +4727,7 @@
         <v>40</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>940</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4739,7 +4739,7 @@
         <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -4754,7 +4754,7 @@
         <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="AJ17" t="n">
         <v>16.5</v>
@@ -4772,7 +4772,7 @@
         <v>4.9</v>
       </c>
       <c r="AO17" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -4805,7 +4805,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
         <v>28</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
         <v>2.44</v>
@@ -884,19 +884,19 @@
         <v>1.32</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -911,7 +911,7 @@
         <v>1.69</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -950,7 +950,7 @@
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -965,55 +965,55 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AU2" t="n">
         <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="BG2" t="n">
         <v>1.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H3" t="n">
         <v>4.7</v>
@@ -1126,67 +1126,67 @@
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X3" t="n">
         <v>27</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -1195,49 +1195,49 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AK3" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO3" t="n">
         <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR3" t="n">
         <v>38</v>
       </c>
       <c r="AS3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU3" t="n">
         <v>10</v>
       </c>
-      <c r="AT3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW3" t="n">
         <v>40</v>
@@ -1255,7 +1255,7 @@
         <v>38</v>
       </c>
       <c r="BB3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC3" t="n">
         <v>14</v>
@@ -1264,16 +1264,16 @@
         <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BI3" t="n">
         <v>3.7</v>
@@ -1282,59 +1282,59 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
         <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -1368,61 +1368,61 @@
         <v>2.06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="H4" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="X4" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Z4" t="n">
         <v>65</v>
@@ -1431,164 +1431,164 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
         <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
         <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR4" t="n">
         <v>22</v>
       </c>
-      <c r="AL4" t="n">
-        <v>210</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BS4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA4" t="n">
         <v>5.4</v>
       </c>
-      <c r="AY4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>3.95</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="H5" t="n">
         <v>2.2</v>
@@ -1649,7 +1649,7 @@
         <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.83</v>
@@ -1658,19 +1658,19 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1685,7 +1685,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC5" t="n">
         <v>95</v>
@@ -1697,10 +1697,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1709,73 +1709,73 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
         <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG5" t="n">
         <v>1.55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G6" t="n">
         <v>1.46</v>
@@ -1882,13 +1882,13 @@
         <v>7.2</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J6" t="n">
         <v>5.4</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.19</v>
@@ -1903,25 +1903,25 @@
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
         <v>1.39</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T6" t="n">
         <v>1.63</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
         <v>3.15</v>
@@ -1930,13 +1930,13 @@
         <v>240</v>
       </c>
       <c r="Y6" t="n">
-        <v>48</v>
+        <v>290</v>
       </c>
       <c r="Z6" t="n">
         <v>450</v>
       </c>
       <c r="AA6" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB6" t="n">
         <v>17</v>
@@ -1945,7 +1945,7 @@
         <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AE6" t="n">
         <v>400</v>
@@ -1957,7 +1957,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AI6" t="n">
         <v>320</v>
@@ -1981,16 +1981,16 @@
         <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -2002,7 +2002,7 @@
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>9.4</v>
@@ -2014,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -2026,7 +2026,7 @@
         <v>19</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
         <v>3.6</v>
@@ -2044,59 +2044,59 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BP6" t="n">
         <v>8.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BR6" t="n">
         <v>18</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU6" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA6" t="n">
         <v>4.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -2187,13 +2187,13 @@
         <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
         <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -2217,7 +2217,7 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
         <v>55</v>
@@ -2268,19 +2268,19 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF7" t="n">
         <v>7.4</v>
@@ -2298,13 +2298,13 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,7 +2316,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2334,7 +2334,7 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2346,11 +2346,11 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
@@ -2414,25 +2414,25 @@
         <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T8" t="n">
         <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X8" t="n">
         <v>12.5</v>
@@ -2459,7 +2459,7 @@
         <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
@@ -2474,10 +2474,10 @@
         <v>36</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -2486,13 +2486,13 @@
         <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>11</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
         <v>19.5</v>
@@ -2522,7 +2522,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB8" t="n">
         <v>30</v>
@@ -2534,13 +2534,13 @@
         <v>38</v>
       </c>
       <c r="BE8" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH8" t="n">
         <v>3.2</v>
@@ -2552,7 +2552,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2570,7 +2570,7 @@
         <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
         <v>1.4</v>
@@ -2659,61 +2659,61 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
@@ -2725,43 +2725,43 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
         <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS9" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
         <v>38</v>
@@ -2770,28 +2770,28 @@
         <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
         <v>40</v>
@@ -2800,19 +2800,19 @@
         <v>3.45</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BN9" t="n">
         <v>4.8</v>
@@ -2821,44 +2821,44 @@
         <v>4.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR9" t="n">
         <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -2907,28 +2907,28 @@
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
         <v>1.8</v>
@@ -2943,7 +2943,7 @@
         <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
         <v>18</v>
@@ -2955,7 +2955,7 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
@@ -2967,10 +2967,10 @@
         <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
@@ -2991,7 +2991,7 @@
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AO10" t="n">
         <v>70</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3015,10 +3015,10 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
@@ -3027,31 +3027,31 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI10" t="n">
         <v>3.1</v>
@@ -3060,31 +3060,31 @@
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN10" t="n">
         <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP10" t="n">
         <v>15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
         <v>7.4</v>
@@ -3093,26 +3093,26 @@
         <v>5.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G11" t="n">
         <v>1.33</v>
@@ -3152,7 +3152,7 @@
         <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="J11" t="n">
         <v>5.7</v>
@@ -3179,7 +3179,7 @@
         <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
         <v>2.42</v>
@@ -3188,7 +3188,7 @@
         <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
@@ -3197,10 +3197,10 @@
         <v>3.95</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z11" t="n">
         <v>150</v>
@@ -3209,16 +3209,16 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>17</v>
       </c>
       <c r="AD11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE11" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF11" t="n">
         <v>8.800000000000001</v>
@@ -3242,13 +3242,13 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
         <v>5.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AP11" t="n">
         <v>18.5</v>
@@ -3275,7 +3275,7 @@
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
@@ -3332,7 +3332,7 @@
         <v>7.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR11" t="n">
         <v>24</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
@@ -3436,7 +3436,7 @@
         <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
         <v>1.6</v>
@@ -3448,13 +3448,13 @@
         <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
@@ -3490,7 +3490,7 @@
         <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
         <v>29</v>
@@ -3553,7 +3553,7 @@
         <v>32</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
         <v>21</v>
@@ -3562,16 +3562,16 @@
         <v>4.3</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BM12" t="n">
         <v>21</v>
@@ -3580,19 +3580,19 @@
         <v>5.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BR12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BT12" t="n">
         <v>7.6</v>
@@ -3601,7 +3601,7 @@
         <v>5.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW12" t="n">
         <v>19</v>
@@ -3613,14 +3613,14 @@
         <v>23</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -3669,19 +3669,19 @@
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
         <v>2.32</v>
@@ -3690,10 +3690,10 @@
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
         <v>1.92</v>
@@ -3720,7 +3720,7 @@
         <v>8.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD13" t="n">
         <v>18.5</v>
@@ -3735,7 +3735,7 @@
         <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>75</v>
@@ -3765,10 +3765,10 @@
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>7</v>
@@ -3780,7 +3780,7 @@
         <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3792,31 +3792,31 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
         <v>5.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>3.05</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
         <v>11</v>
@@ -3843,7 +3843,7 @@
         <v>7.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
         <v>9.199999999999999</v>
@@ -3867,14 +3867,14 @@
         <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>2.4</v>
       </c>
       <c r="I14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3929,31 +3929,31 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W14" t="n">
         <v>1.51</v>
@@ -3962,22 +3962,22 @@
         <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z14" t="n">
         <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>23</v>
@@ -3995,7 +3995,7 @@
         <v>29</v>
       </c>
       <c r="AJ14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
         <v>28</v>
@@ -4010,13 +4010,13 @@
         <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>17</v>
@@ -4025,7 +4025,7 @@
         <v>29</v>
       </c>
       <c r="AT14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU14" t="n">
         <v>8.800000000000001</v>
@@ -4034,7 +4034,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX14" t="n">
         <v>20</v>
@@ -4046,7 +4046,7 @@
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB14" t="n">
         <v>38</v>
@@ -4061,7 +4061,7 @@
         <v>46</v>
       </c>
       <c r="BF14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG14" t="n">
         <v>11</v>
@@ -4070,7 +4070,7 @@
         <v>4.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14" t="n">
         <v>8.800000000000001</v>
@@ -4079,56 +4079,56 @@
         <v>6.2</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM14" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="BN14" t="n">
         <v>6.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP14" t="n">
         <v>20</v>
       </c>
       <c r="BQ14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BR14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV14" t="n">
         <v>17</v>
       </c>
       <c r="BW14" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX14" t="n">
         <v>24</v>
       </c>
       <c r="BY14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
         <v>5.3</v>
@@ -4189,10 +4189,10 @@
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R15" t="n">
         <v>1.91</v>
@@ -4201,16 +4201,16 @@
         <v>2.04</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X15" t="n">
         <v>38</v>
@@ -4219,10 +4219,10 @@
         <v>42</v>
       </c>
       <c r="Z15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
         <v>15</v>
@@ -4237,7 +4237,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
@@ -4249,7 +4249,7 @@
         <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK15" t="n">
         <v>14.5</v>
@@ -4267,7 +4267,7 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ15" t="n">
         <v>36</v>
@@ -4285,16 +4285,16 @@
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>16.5</v>
@@ -4315,22 +4315,22 @@
         <v>55</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BH15" t="n">
         <v>5.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BL15" t="n">
         <v>75</v>
@@ -4348,19 +4348,19 @@
         <v>9</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR15" t="n">
         <v>18</v>
       </c>
       <c r="BS15" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT15" t="n">
         <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BV15" t="n">
         <v>44</v>
@@ -4372,17 +4372,17 @@
         <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BZ15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G16" t="n">
         <v>2.02</v>
@@ -4452,16 +4452,16 @@
         <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
         <v>1.98</v>
@@ -4542,7 +4542,7 @@
         <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
         <v>12</v>
@@ -4554,7 +4554,7 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
         <v>20</v>
@@ -4584,7 +4584,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
         <v>7.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
         <v>3.1</v>
@@ -4706,13 +4706,13 @@
         <v>1.85</v>
       </c>
       <c r="S17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T17" t="n">
         <v>1.59</v>
       </c>
       <c r="U17" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
@@ -4721,10 +4721,10 @@
         <v>2.84</v>
       </c>
       <c r="X17" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="Y17" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Z17" t="n">
         <v>940</v>
@@ -4754,7 +4754,7 @@
         <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
         <v>16.5</v>
@@ -4808,7 +4808,7 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB17" t="n">
         <v>13.5</v>
@@ -4847,10 +4847,10 @@
         <v>21</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP17" t="n">
         <v>13</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 22:20:35</t>
+          <t>2026-07-16 00:33:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,175 +857,175 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="G2" t="n">
         <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.31</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>1.52</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
         <v>1.69</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF2" t="n">
         <v>970</v>
       </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="AU2" t="n">
         <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.09</v>
+        <v>1.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
         <v>1.01</v>
@@ -1037,25 +1037,25 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO2" t="n">
         <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS2" t="n">
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1111,31 +1111,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="n">
         <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
@@ -1144,28 +1144,28 @@
         <v>2.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S3" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
         <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="n">
         <v>27</v>
@@ -1177,7 +1177,7 @@
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
@@ -1186,7 +1186,7 @@
         <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -1198,13 +1198,13 @@
         <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ3" t="n">
         <v>20</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
@@ -1213,28 +1213,28 @@
         <v>60</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO3" t="n">
         <v>38</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR3" t="n">
         <v>38</v>
       </c>
       <c r="AS3" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AT3" t="n">
         <v>12.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
         <v>17.5</v>
@@ -1243,25 +1243,25 @@
         <v>40</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE3" t="n">
         <v>48</v>
@@ -1273,7 +1273,7 @@
         <v>29</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI3" t="n">
         <v>3.7</v>
@@ -1282,13 +1282,13 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
@@ -1300,41 +1300,41 @@
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
         <v>19</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3" t="n">
         <v>34</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="U4" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
         <v>38</v>
@@ -1431,164 +1431,164 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
         <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>27</v>
+        <v>210</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.4</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.2</v>
+        <v>1.52</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.1</v>
+        <v>1.49</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.8</v>
+        <v>1.53</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.5</v>
+        <v>1.47</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>1.42</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.5</v>
+        <v>1.51</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.3</v>
+        <v>1.52</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.6</v>
+        <v>1.48</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.1</v>
+        <v>1.48</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>1.46</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>1.52</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.2</v>
+        <v>1.52</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>1.51</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>1.54</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.9</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>17.5</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
         <v>2.2</v>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.27</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1670,7 +1670,7 @@
         <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1873,52 +1873,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="G6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K6" t="n">
         <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q6" t="n">
         <v>1.39</v>
       </c>
       <c r="R6" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="S6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -1930,22 +1930,22 @@
         <v>240</v>
       </c>
       <c r="Y6" t="n">
-        <v>290</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="n">
         <v>450</v>
       </c>
       <c r="AA6" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE6" t="n">
         <v>400</v>
@@ -1954,88 +1954,88 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL6" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
         <v>260</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
       </c>
       <c r="AP6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV6" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AW6" t="n">
         <v>8.6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AX6" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="BG6" t="n">
         <v>10.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI6" t="n">
         <v>4.7</v>
@@ -2050,19 +2050,19 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>4.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
         <v>18</v>
@@ -2074,7 +2074,7 @@
         <v>12</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2089,14 +2089,14 @@
         <v>8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I7" t="n">
         <v>2.54</v>
@@ -2142,10 +2142,10 @@
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
@@ -2154,31 +2154,31 @@
         <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
         <v>13.5</v>
@@ -2196,25 +2196,25 @@
         <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
         <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AJ7" t="n">
         <v>65</v>
@@ -2229,10 +2229,10 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
@@ -2268,19 +2268,19 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
         <v>7.4</v>
@@ -2289,68 +2289,68 @@
         <v>16.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2399,13 +2399,13 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.37</v>
@@ -2414,19 +2414,19 @@
         <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
         <v>1.43</v>
@@ -2441,22 +2441,22 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
         <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF8" t="n">
         <v>15</v>
@@ -2465,13 +2465,13 @@
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI8" t="n">
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
@@ -2483,10 +2483,10 @@
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP8" t="n">
         <v>11.5</v>
@@ -2501,7 +2501,7 @@
         <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2513,13 +2513,13 @@
         <v>34</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>46</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN8" t="n">
         <v>5.3</v>
@@ -2567,7 +2567,7 @@
         <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>9</v>
@@ -2588,7 +2588,7 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>2.14</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2653,13 +2653,13 @@
         <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
@@ -2674,22 +2674,22 @@
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
         <v>14.5</v>
@@ -2701,13 +2701,13 @@
         <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>44</v>
@@ -2719,7 +2719,7 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
@@ -2734,7 +2734,7 @@
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN9" t="n">
         <v>17</v>
@@ -2755,7 +2755,7 @@
         <v>60</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
         <v>7.8</v>
@@ -2767,16 +2767,16 @@
         <v>38</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB9" t="n">
         <v>24</v>
@@ -2797,7 +2797,7 @@
         <v>40</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI9" t="n">
         <v>2.94</v>
@@ -2806,13 +2806,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.8</v>
@@ -2824,13 +2824,13 @@
         <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR9" t="n">
         <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT9" t="n">
         <v>6.8</v>
@@ -2842,23 +2842,23 @@
         <v>29</v>
       </c>
       <c r="BW9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
         <v>44</v>
       </c>
       <c r="BY9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ9" t="n">
         <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
         <v>2.1</v>
@@ -2904,37 +2904,37 @@
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
         <v>1.28</v>
@@ -2943,7 +2943,7 @@
         <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
         <v>18</v>
@@ -2955,7 +2955,7 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
@@ -2964,7 +2964,7 @@
         <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
         <v>13.5</v>
@@ -2991,7 +2991,7 @@
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>70</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS10" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3015,40 +3015,40 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF10" t="n">
         <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.35</v>
@@ -3060,16 +3060,16 @@
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>16</v>
-      </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO10" t="n">
         <v>3.8</v>
@@ -3078,41 +3078,41 @@
         <v>15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV10" t="n">
         <v>34</v>
       </c>
       <c r="BW10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA10" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3143,58 +3143,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G11" t="n">
         <v>1.33</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I11" t="n">
         <v>15.5</v>
       </c>
       <c r="J11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
         <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="X11" t="n">
         <v>28</v>
@@ -3203,52 +3203,52 @@
         <v>46</v>
       </c>
       <c r="Z11" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD11" t="n">
         <v>55</v>
       </c>
       <c r="AE11" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI11" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AJ11" t="n">
         <v>11.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN11" t="n">
         <v>5.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="AP11" t="n">
         <v>18.5</v>
@@ -3263,7 +3263,7 @@
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -3275,7 +3275,7 @@
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
@@ -3302,16 +3302,16 @@
         <v>3.95</v>
       </c>
       <c r="BG11" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BI11" t="n">
         <v>3.55</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK11" t="n">
         <v>9.6</v>
@@ -3323,22 +3323,22 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BT11" t="n">
         <v>16</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3397,37 +3397,37 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
         <v>2.08</v>
       </c>
       <c r="H12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I12" t="n">
         <v>3.75</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.85</v>
-      </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
         <v>1.68</v>
@@ -3436,25 +3436,25 @@
         <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
@@ -3466,13 +3466,13 @@
         <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
         <v>15</v>
@@ -3481,10 +3481,10 @@
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ12" t="n">
         <v>26</v>
@@ -3493,134 +3493,134 @@
         <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN12" t="n">
         <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AS12" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BE12" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BH12" t="n">
         <v>4.3</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM12" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BN12" t="n">
         <v>5.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP12" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BT12" t="n">
         <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BX12" t="n">
         <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3654,175 +3654,175 @@
         <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="n">
         <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
         <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
         <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA13" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC13" t="n">
         <v>7.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG13" t="n">
         <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
         <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO13" t="n">
         <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT13" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3831,13 +3831,13 @@
         <v>11.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>7.4</v>
@@ -3846,35 +3846,35 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BX13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
         <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3923,7 +3923,7 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3935,7 +3935,7 @@
         <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
         <v>1.56</v>
@@ -3944,16 +3944,16 @@
         <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.51</v>
       </c>
       <c r="U14" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W14" t="n">
         <v>1.51</v>
@@ -3965,10 +3965,10 @@
         <v>17</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="n">
         <v>19</v>
@@ -3980,7 +3980,7 @@
         <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
         <v>24</v>
@@ -3992,7 +3992,7 @@
         <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ14" t="n">
         <v>48</v>
@@ -4028,7 +4028,7 @@
         <v>16.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
@@ -4037,7 +4037,7 @@
         <v>19</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
@@ -4064,10 +4064,10 @@
         <v>14.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI14" t="n">
         <v>3.5</v>
@@ -4082,13 +4082,13 @@
         <v>75</v>
       </c>
       <c r="BM14" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BN14" t="n">
         <v>6.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
         <v>20</v>
@@ -4100,16 +4100,16 @@
         <v>26</v>
       </c>
       <c r="BS14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW14" t="n">
         <v>11.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>1.47</v>
       </c>
       <c r="G15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>5.3</v>
@@ -4189,31 +4189,31 @@
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y15" t="n">
         <v>42</v>
@@ -4222,10 +4222,10 @@
         <v>75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC15" t="n">
         <v>13.5</v>
@@ -4234,13 +4234,13 @@
         <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="n">
         <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>18.5</v>
@@ -4291,13 +4291,13 @@
         <v>34</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
         <v>50</v>
@@ -4312,16 +4312,16 @@
         <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI15" t="n">
         <v>4.3</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -4425,10 +4425,10 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.35</v>
@@ -4437,34 +4437,34 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4479,7 +4479,7 @@
         <v>90</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC16" t="n">
         <v>10.5</v>
@@ -4491,7 +4491,7 @@
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
@@ -4521,16 +4521,16 @@
         <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="AQ16" t="n">
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
         <v>12</v>
@@ -4554,25 +4554,25 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
         <v>3.8</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
@@ -4697,37 +4697,37 @@
         <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
         <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S17" t="n">
         <v>2.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V17" t="n">
         <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y17" t="n">
         <v>65</v>
       </c>
       <c r="Z17" t="n">
-        <v>940</v>
+        <v>840</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4736,7 +4736,7 @@
         <v>15.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>36</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
@@ -4757,7 +4757,7 @@
         <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK17" t="n">
         <v>14</v>
@@ -4769,7 +4769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO17" t="n">
         <v>260</v>
@@ -4805,7 +4805,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
         <v>44</v>
@@ -4823,22 +4823,22 @@
         <v>30</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
         <v>28</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4847,50 +4847,50 @@
         <v>21</v>
       </c>
       <c r="BN17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>6.6</v>
       </c>
-      <c r="BO17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BR17" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="BS17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>10.5</v>
       </c>
-      <c r="BT17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>14.5</v>
-      </c>
       <c r="CA17" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
         <v>1.59</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
@@ -899,178 +899,178 @@
         <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>42</v>
       </c>
-      <c r="AD2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>210</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>900</v>
-      </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
         <v>160</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.64</v>
+        <v>5.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.75</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.79</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.79</v>
+        <v>4.1</v>
       </c>
       <c r="AU2" t="n">
         <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.76</v>
+        <v>6.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.78</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.65</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.74</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.78</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.69</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.78</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.69</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.79</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
         <v>2.66</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BN2" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BR2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H3" t="n">
         <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -1129,7 +1129,7 @@
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1141,52 +1141,52 @@
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -1195,16 +1195,16 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
@@ -1213,13 +1213,13 @@
         <v>60</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
         <v>24</v>
@@ -1234,82 +1234,82 @@
         <v>12.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
         <v>17.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
         <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BF3" t="n">
         <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
         <v>6</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU3" t="n">
         <v>5.8</v>
@@ -1318,23 +1318,23 @@
         <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
         <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="R4" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="T4" t="n">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="X4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE4" t="n">
         <v>500</v>
       </c>
-      <c r="Y4" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>75</v>
       </c>
-      <c r="AF4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>900</v>
-      </c>
       <c r="AK4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>210</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>85</v>
+        <v>9.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>220</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.52</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.49</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.51</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.53</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.47</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.51</v>
+        <v>5.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.48</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.48</v>
+        <v>5.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.46</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.52</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.51</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.54</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.54</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>19.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1619,175 +1619,175 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L5" t="n">
         <v>1.4</v>
       </c>
-      <c r="G5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.28</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.85</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U5" t="n">
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>500</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>95</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,31 +1799,31 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
@@ -1835,14 +1835,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
         <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
@@ -1900,52 +1900,52 @@
         <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q6" t="n">
         <v>1.39</v>
       </c>
       <c r="R6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="X6" t="n">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="Y6" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="Z6" t="n">
         <v>450</v>
       </c>
       <c r="AA6" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AE6" t="n">
         <v>400</v>
@@ -1957,85 +1957,85 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
         <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
         <v>260</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI6" t="n">
         <v>4.7</v>
@@ -2050,31 +2050,31 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS6" t="n">
         <v>6.2</v>
       </c>
       <c r="BT6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BU6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2089,14 +2089,14 @@
         <v>8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H7" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.44</v>
@@ -2154,10 +2154,10 @@
         <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
         <v>2.06</v>
@@ -2169,28 +2169,28 @@
         <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W7" t="n">
         <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
         <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
         <v>12.5</v>
@@ -2199,19 +2199,19 @@
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
         <v>29</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
         <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
         <v>42</v>
@@ -2220,7 +2220,7 @@
         <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -2235,13 +2235,13 @@
         <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
         <v>14.5</v>
@@ -2250,16 +2250,16 @@
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AW7" t="n">
         <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
         <v>12</v>
@@ -2268,28 +2268,28 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
         <v>7.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI7" t="n">
         <v>2.64</v>
@@ -2298,16 +2298,16 @@
         <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO7" t="n">
         <v>5.5</v>
@@ -2316,16 +2316,16 @@
         <v>28</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU7" t="n">
         <v>4.5</v>
@@ -2334,23 +2334,23 @@
         <v>19</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BX7" t="n">
         <v>34</v>
       </c>
       <c r="BY7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>8</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2381,73 +2381,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
         <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.14</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y8" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>12</v>
-      </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
         <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
@@ -2456,7 +2456,7 @@
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
         <v>15</v>
@@ -2465,28 +2465,28 @@
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
         <v>100</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP8" t="n">
         <v>11.5</v>
@@ -2516,67 +2516,67 @@
         <v>13.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB8" t="n">
         <v>30</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BF8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO8" t="n">
         <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BZ8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2665,13 +2665,13 @@
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
         <v>3.55</v>
@@ -2680,7 +2680,7 @@
         <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
         <v>1.35</v>
@@ -2692,19 +2692,19 @@
         <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA9" t="n">
         <v>75</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>15</v>
@@ -2716,7 +2716,7 @@
         <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
         <v>18</v>
@@ -2734,7 +2734,7 @@
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
         <v>17</v>
@@ -2749,25 +2749,25 @@
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT9" t="n">
         <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
         <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
@@ -2797,68 +2797,68 @@
         <v>40</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BN9" t="n">
         <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
         <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BR9" t="n">
         <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BT9" t="n">
         <v>6.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV9" t="n">
         <v>29</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX9" t="n">
         <v>44</v>
       </c>
       <c r="BY9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BZ9" t="n">
         <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
         <v>2.1</v>
@@ -2904,7 +2904,7 @@
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.43</v>
@@ -2913,43 +2913,43 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
         <v>2.04</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
         <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
         <v>110</v>
@@ -2961,13 +2961,13 @@
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2976,7 +2976,7 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>32</v>
@@ -2985,134 +2985,134 @@
         <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AO10" t="n">
         <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA10" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BB10" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
         <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="n">
         <v>3.35</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
         <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX10" t="n">
         <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>30</v>
       </c>
       <c r="CA10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
         <v>1.33</v>
@@ -3152,10 +3152,10 @@
         <v>12.5</v>
       </c>
       <c r="I11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K11" t="n">
         <v>7</v>
@@ -3167,22 +3167,22 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
         <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
         <v>2.12</v>
@@ -3197,13 +3197,13 @@
         <v>4</v>
       </c>
       <c r="X11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="n">
         <v>46</v>
       </c>
       <c r="Z11" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -3218,40 +3218,40 @@
         <v>55</v>
       </c>
       <c r="AE11" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
         <v>11.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AP11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.03</v>
@@ -3263,7 +3263,7 @@
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -3275,7 +3275,7 @@
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
@@ -3287,7 +3287,7 @@
         <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
         <v>11</v>
@@ -3299,13 +3299,13 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI11" t="n">
         <v>3.55</v>
@@ -3323,22 +3323,22 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR11" t="n">
         <v>24</v>
       </c>
       <c r="BS11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BT11" t="n">
         <v>16</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
         <v>3.65</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -3436,19 +3436,19 @@
         <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
         <v>2.54</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -3466,7 +3466,7 @@
         <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>15.5</v>
@@ -3484,13 +3484,13 @@
         <v>15.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
         <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>28</v>
@@ -3505,10 +3505,10 @@
         <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR12" t="n">
         <v>25</v>
@@ -3526,13 +3526,13 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX12" t="n">
         <v>13.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
         <v>14.5</v>
@@ -3556,25 +3556,25 @@
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="BJ12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL12" t="n">
         <v>85</v>
       </c>
       <c r="BM12" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BN12" t="n">
         <v>5.3</v>
@@ -3586,41 +3586,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR12" t="n">
         <v>24</v>
       </c>
       <c r="BS12" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV12" t="n">
         <v>27</v>
       </c>
       <c r="BW12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BX12" t="n">
         <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BZ12" t="n">
         <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
         <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.05</v>
@@ -3672,28 +3672,28 @@
         <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
         <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
         <v>1.92</v>
@@ -3702,34 +3702,34 @@
         <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC13" t="n">
         <v>7.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
         <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG13" t="n">
         <v>13</v>
@@ -3738,16 +3738,16 @@
         <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK13" t="n">
         <v>34</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
@@ -3765,13 +3765,13 @@
         <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
@@ -3780,7 +3780,7 @@
         <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
         <v>11.5</v>
@@ -3789,37 +3789,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
         <v>8.199999999999999</v>
@@ -3831,7 +3831,7 @@
         <v>11.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO13" t="n">
         <v>4.3</v>
@@ -3840,10 +3840,10 @@
         <v>18.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS13" t="n">
         <v>9.4</v>
@@ -3855,26 +3855,26 @@
         <v>5.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY13" t="n">
         <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA13" t="n">
         <v>9.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.94</v>
       </c>
       <c r="H14" t="n">
         <v>2.42</v>
@@ -3929,40 +3929,40 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="T14" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="U14" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
         <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z14" t="n">
         <v>20</v>
@@ -3971,10 +3971,10 @@
         <v>36</v>
       </c>
       <c r="AB14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
@@ -3983,49 +3983,49 @@
         <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI14" t="n">
         <v>27</v>
       </c>
       <c r="AJ14" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AK14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM14" t="n">
         <v>55</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ14" t="n">
         <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>29</v>
       </c>
       <c r="AT14" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU14" t="n">
         <v>9</v>
@@ -4034,13 +4034,13 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX14" t="n">
         <v>22</v>
       </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
         <v>13</v>
@@ -4055,13 +4055,13 @@
         <v>24</v>
       </c>
       <c r="BD14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE14" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BF14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG14" t="n">
         <v>10.5</v>
@@ -4070,25 +4070,25 @@
         <v>4.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BJ14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM14" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="BN14" t="n">
         <v>6.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP14" t="n">
         <v>20</v>
@@ -4106,7 +4106,7 @@
         <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV14" t="n">
         <v>16.5</v>
@@ -4115,20 +4115,20 @@
         <v>11.5</v>
       </c>
       <c r="BX14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY14" t="n">
         <v>16.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA14" t="n">
         <v>11</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4201,10 +4201,10 @@
         <v>2.06</v>
       </c>
       <c r="T15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
@@ -4222,19 +4222,19 @@
         <v>75</v>
       </c>
       <c r="AA15" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD15" t="n">
         <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="n">
         <v>12.5</v>
@@ -4243,7 +4243,7 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
         <v>65</v>
@@ -4267,7 +4267,7 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ15" t="n">
         <v>36</v>
@@ -4285,10 +4285,10 @@
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX15" t="n">
         <v>11.5</v>
@@ -4303,13 +4303,13 @@
         <v>50</v>
       </c>
       <c r="BB15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC15" t="n">
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE15" t="n">
         <v>50</v>
@@ -4318,71 +4318,71 @@
         <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BL15" t="n">
         <v>75</v>
       </c>
       <c r="BM15" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="BN15" t="n">
         <v>4.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP15" t="n">
         <v>9</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR15" t="n">
         <v>18</v>
       </c>
       <c r="BS15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT15" t="n">
         <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BV15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW15" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BZ15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -4425,7 +4425,7 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -4443,10 +4443,10 @@
         <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
@@ -4458,25 +4458,25 @@
         <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB16" t="n">
         <v>12.5</v>
@@ -4485,25 +4485,25 @@
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
         <v>23</v>
@@ -4515,85 +4515,85 @@
         <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AO16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP16" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU16" t="n">
         <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO16" t="n">
         <v>4.3</v>
@@ -4602,25 +4602,25 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR16" t="n">
         <v>25</v>
       </c>
       <c r="BS16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT16" t="n">
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
       </c>
       <c r="BW16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4629,14 +4629,14 @@
         <v>12</v>
       </c>
       <c r="BZ16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4676,10 +4676,10 @@
         <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K17" t="n">
         <v>5.4</v>
@@ -4691,7 +4691,7 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.14</v>
@@ -4703,67 +4703,67 @@
         <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
         <v>2.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="X17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE17" t="n">
         <v>70</v>
       </c>
-      <c r="Y17" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>840</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AF17" t="n">
         <v>13</v>
       </c>
-      <c r="AD17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -4772,46 +4772,46 @@
         <v>4.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>260</v>
+        <v>44</v>
       </c>
       <c r="AP17" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AR17" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AS17" t="n">
         <v>44</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW17" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AX17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB17" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
         <v>12.5</v>
@@ -4820,13 +4820,13 @@
         <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BH17" t="n">
         <v>5.4</v>
@@ -4835,16 +4835,16 @@
         <v>4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BN17" t="n">
         <v>4.9</v>
@@ -4853,44 +4853,44 @@
         <v>4.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR17" t="n">
         <v>18.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BZ17" t="n">
         <v>10.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.6</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.59</v>
-      </c>
       <c r="P2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
@@ -899,130 +899,130 @@
         <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="V2" t="n">
         <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>1.67</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>1.49</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AU2" t="n">
         <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.2</v>
+        <v>1.68</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>1.49</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>1.68</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.8</v>
+        <v>1.66</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.4</v>
+        <v>1.69</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.8</v>
+        <v>1.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2" t="n">
         <v>12.5</v>
@@ -1046,25 +1046,25 @@
         <v>25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.97</v>
+        <v>7.6</v>
       </c>
       <c r="BR2" t="n">
         <v>55</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
         <v>38</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.02</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1117,55 +1117,55 @@
         <v>1.77</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V3" t="n">
         <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y3" t="n">
         <v>26</v>
@@ -1177,13 +1177,13 @@
         <v>95</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE3" t="n">
         <v>46</v>
@@ -1204,13 +1204,13 @@
         <v>19</v>
       </c>
       <c r="AK3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN3" t="n">
         <v>6.6</v>
@@ -1219,10 +1219,10 @@
         <v>32</v>
       </c>
       <c r="AP3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>25</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>24</v>
       </c>
       <c r="AR3" t="n">
         <v>38</v>
@@ -1231,13 +1231,13 @@
         <v>85</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>42</v>
@@ -1270,25 +1270,25 @@
         <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>70</v>
       </c>
       <c r="BM3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.9</v>
@@ -1300,41 +1300,41 @@
         <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BR3" t="n">
         <v>19.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1365,82 +1365,82 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z4" t="n">
         <v>75</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
         <v>16.5</v>
@@ -1449,7 +1449,7 @@
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1458,91 +1458,91 @@
         <v>75</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
         <v>210</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO4" t="n">
         <v>220</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.9</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
         <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="n">
         <v>4.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
@@ -1551,7 +1551,7 @@
         <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>5.8</v>
@@ -1560,35 +1560,35 @@
         <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT4" t="n">
         <v>8</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV4" t="n">
         <v>27</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA4" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.4</v>
@@ -1643,28 +1643,28 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.12</v>
+        <v>1.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
         <v>1.17</v>
@@ -1673,22 +1673,22 @@
         <v>2.22</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>25</v>
@@ -1709,82 +1709,82 @@
         <v>240</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="n">
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
         <v>160</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS5" t="n">
         <v>7</v>
       </c>
-      <c r="AS5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AT5" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
@@ -1811,7 +1811,7 @@
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
@@ -1829,20 +1829,20 @@
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="G6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K6" t="n">
         <v>6.4</v>
@@ -1906,52 +1906,52 @@
         <v>3.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S6" t="n">
         <v>1.98</v>
       </c>
       <c r="T6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="X6" t="n">
         <v>95</v>
       </c>
       <c r="Y6" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="n">
         <v>450</v>
       </c>
       <c r="AA6" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AE6" t="n">
         <v>400</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
@@ -1960,10 +1960,10 @@
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
         <v>14.5</v>
@@ -1975,7 +1975,7 @@
         <v>260</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
@@ -1990,34 +1990,34 @@
         <v>28</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT6" t="n">
         <v>12.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AX6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
@@ -2026,16 +2026,16 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>46</v>
       </c>
-      <c r="BF6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>42</v>
-      </c>
       <c r="BH6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI6" t="n">
         <v>4.7</v>
@@ -2044,34 +2044,34 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU6" t="n">
         <v>9.199999999999999</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>3.25</v>
       </c>
       <c r="G7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.55</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.44</v>
@@ -2157,7 +2157,7 @@
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
         <v>2.06</v>
@@ -2172,37 +2172,37 @@
         <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
         <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
         <v>25</v>
@@ -2214,25 +2214,25 @@
         <v>19</v>
       </c>
       <c r="AI7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
         <v>11</v>
@@ -2241,10 +2241,10 @@
         <v>8.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -2253,13 +2253,13 @@
         <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AY7" t="n">
         <v>12</v>
@@ -2268,89 +2268,89 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BC7" t="n">
         <v>32</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>75</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BG7" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
         <v>3.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO7" t="n">
         <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
         <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU7" t="n">
         <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>30</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
         <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.44</v>
@@ -2405,37 +2405,37 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
         <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
         <v>12.5</v>
@@ -2447,13 +2447,13 @@
         <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE8" t="n">
         <v>85</v>
@@ -2471,25 +2471,25 @@
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
         <v>100</v>
       </c>
       <c r="AM8" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
         <v>48</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2501,7 +2501,7 @@
         <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2516,7 +2516,7 @@
         <v>13.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
@@ -2531,16 +2531,16 @@
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BH8" t="n">
         <v>3.25</v>
@@ -2552,7 +2552,7 @@
         <v>9.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2641,37 +2641,37 @@
         <v>2.16</v>
       </c>
       <c r="H9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.75</v>
       </c>
       <c r="L9" t="n">
         <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
         <v>3.55</v>
@@ -2692,7 +2692,7 @@
         <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>27</v>
@@ -2707,7 +2707,7 @@
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE9" t="n">
         <v>44</v>
@@ -2719,19 +2719,19 @@
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>95</v>
@@ -2740,7 +2740,7 @@
         <v>17</v>
       </c>
       <c r="AO9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP9" t="n">
         <v>13</v>
@@ -2779,25 +2779,25 @@
         <v>48</v>
       </c>
       <c r="BB9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC9" t="n">
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BF9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
         <v>40</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI9" t="n">
         <v>3.2</v>
@@ -2818,19 +2818,19 @@
         <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP9" t="n">
         <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BR9" t="n">
         <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BT9" t="n">
         <v>6.8</v>
@@ -2839,26 +2839,26 @@
         <v>6.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
         <v>44</v>
       </c>
       <c r="BY9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BZ9" t="n">
         <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2892,25 +2892,25 @@
         <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.43</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
         <v>3.85</v>
@@ -2919,28 +2919,28 @@
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
         <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
         <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
@@ -2955,7 +2955,7 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
@@ -2964,10 +2964,10 @@
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2985,28 +2985,28 @@
         <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO10" t="n">
         <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3015,104 +3015,104 @@
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>15.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BD10" t="n">
         <v>30</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
         <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH10" t="n">
         <v>3.35</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT10" t="n">
         <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3146,112 +3146,112 @@
         <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
         <v>4</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
         <v>46</v>
       </c>
       <c r="Z11" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AE11" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI11" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.03</v>
@@ -3263,7 +3263,7 @@
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -3287,10 +3287,10 @@
         <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD11" t="n">
         <v>1.03</v>
@@ -3299,22 +3299,22 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>240</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,10 +3323,10 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BP11" t="n">
         <v>7.4</v>
@@ -3335,16 +3335,16 @@
         <v>5.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT11" t="n">
         <v>17</v>
       </c>
-      <c r="BT11" t="n">
-        <v>16</v>
-      </c>
       <c r="BU11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3356,17 +3356,17 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CA11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K12" t="n">
         <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.32</v>
@@ -3427,28 +3427,28 @@
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
         <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -3457,10 +3457,10 @@
         <v>19.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
         <v>13.5</v>
@@ -3469,13 +3469,13 @@
         <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
         <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
@@ -3490,7 +3490,7 @@
         <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AL12" t="n">
         <v>28</v>
@@ -3508,40 +3508,40 @@
         <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR12" t="n">
         <v>25</v>
       </c>
       <c r="AS12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT12" t="n">
         <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX12" t="n">
         <v>13.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC12" t="n">
         <v>17</v>
@@ -3550,77 +3550,77 @@
         <v>25</v>
       </c>
       <c r="BE12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL12" t="n">
         <v>85</v>
       </c>
       <c r="BM12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS12" t="n">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BV12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BX12" t="n">
         <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
         <v>3.9</v>
@@ -3663,10 +3663,10 @@
         <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.5</v>
@@ -3681,10 +3681,10 @@
         <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
@@ -3699,10 +3699,10 @@
         <v>1.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -3816,7 +3816,7 @@
         <v>3.05</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="BJ13" t="n">
         <v>11</v>
@@ -3840,7 +3840,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR13" t="n">
         <v>38</v>
@@ -3852,16 +3852,16 @@
         <v>7</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV13" t="n">
         <v>36</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
         <v>10</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>2.88</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H14" t="n">
         <v>2.42</v>
       </c>
       <c r="I14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3923,7 +3923,7 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3935,46 +3935,46 @@
         <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S14" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y14" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
         <v>36</v>
       </c>
       <c r="AB14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
@@ -3995,28 +3995,28 @@
         <v>27</v>
       </c>
       <c r="AJ14" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>16</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>18</v>
@@ -4028,7 +4028,7 @@
         <v>17.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
@@ -4043,16 +4043,16 @@
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
         <v>38</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD14" t="n">
         <v>26</v>
@@ -4061,19 +4061,19 @@
         <v>42</v>
       </c>
       <c r="BF14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK14" t="n">
         <v>7.2</v>
@@ -4082,7 +4082,7 @@
         <v>70</v>
       </c>
       <c r="BM14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BN14" t="n">
         <v>6.8</v>
@@ -4091,16 +4091,16 @@
         <v>5</v>
       </c>
       <c r="BP14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ14" t="n">
         <v>14</v>
       </c>
       <c r="BR14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
@@ -4109,7 +4109,7 @@
         <v>5.1</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW14" t="n">
         <v>11.5</v>
@@ -4118,17 +4118,17 @@
         <v>23</v>
       </c>
       <c r="BY14" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BZ14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA14" t="n">
         <v>11</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>1.47</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I15" t="n">
         <v>7.4</v>
@@ -4195,7 +4195,7 @@
         <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S15" t="n">
         <v>2.06</v>
@@ -4213,7 +4213,7 @@
         <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y15" t="n">
         <v>42</v>
@@ -4228,7 +4228,7 @@
         <v>15</v>
       </c>
       <c r="AC15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
         <v>27</v>
@@ -4267,7 +4267,7 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ15" t="n">
         <v>36</v>
@@ -4288,13 +4288,13 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>17</v>
@@ -4303,7 +4303,7 @@
         <v>50</v>
       </c>
       <c r="BB15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC15" t="n">
         <v>13</v>
@@ -4315,13 +4315,13 @@
         <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG15" t="n">
         <v>42</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI15" t="n">
         <v>4.2</v>
@@ -4330,7 +4330,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BL15" t="n">
         <v>75</v>
@@ -4348,25 +4348,25 @@
         <v>9</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR15" t="n">
         <v>18</v>
       </c>
       <c r="BS15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT15" t="n">
         <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV15" t="n">
         <v>46</v>
       </c>
       <c r="BW15" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BX15" t="n">
         <v>42</v>
@@ -4375,14 +4375,14 @@
         <v>29</v>
       </c>
       <c r="BZ15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -4425,16 +4425,16 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
         <v>4.6</v>
@@ -4443,16 +4443,16 @@
         <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
         <v>1.71</v>
@@ -4464,13 +4464,13 @@
         <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="n">
         <v>34</v>
@@ -4485,7 +4485,7 @@
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
         <v>55</v>
@@ -4521,16 +4521,16 @@
         <v>50</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>15.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
@@ -4542,7 +4542,7 @@
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -4554,7 +4554,7 @@
         <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB16" t="n">
         <v>19.5</v>
@@ -4563,19 +4563,19 @@
         <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF16" t="n">
         <v>8.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI16" t="n">
         <v>3.15</v>
@@ -4584,13 +4584,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN16" t="n">
         <v>4.8</v>
@@ -4602,41 +4602,41 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR16" t="n">
         <v>25</v>
       </c>
       <c r="BS16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT16" t="n">
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H17" t="n">
         <v>6.2</v>
@@ -4706,7 +4706,7 @@
         <v>1.87</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T17" t="n">
         <v>1.59</v>
@@ -4718,7 +4718,7 @@
         <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="X17" t="n">
         <v>34</v>
@@ -4736,7 +4736,7 @@
         <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>25</v>
@@ -4754,13 +4754,13 @@
         <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>280</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
@@ -4769,19 +4769,19 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO17" t="n">
         <v>44</v>
       </c>
       <c r="AP17" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AQ17" t="n">
         <v>30</v>
       </c>
       <c r="AR17" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
         <v>44</v>
@@ -4802,10 +4802,10 @@
         <v>12</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA17" t="n">
         <v>48</v>
@@ -4835,7 +4835,7 @@
         <v>4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK17" t="n">
         <v>7</v>
@@ -4844,53 +4844,53 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR17" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU17" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV17" t="n">
         <v>42</v>
       </c>
       <c r="BW17" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>10.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,172 +857,172 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="L2" t="n">
         <v>1.63</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="O2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.6</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.57</v>
-      </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK2" t="n">
         <v>42</v>
       </c>
-      <c r="AD2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>500</v>
-      </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.67</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.49</v>
+        <v>27</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.68</v>
+        <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.69</v>
+        <v>42</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.7</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.49</v>
+        <v>19.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.68</v>
+        <v>30</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.69</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.55</v>
+        <v>36</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>12.5</v>
@@ -1034,16 +1034,16 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.12</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
         <v>7.6</v>
@@ -1052,13 +1052,13 @@
         <v>55</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>38</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.06</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
         <v>1.77</v>
@@ -1120,13 +1120,13 @@
         <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -1135,28 +1135,28 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q3" t="n">
         <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
         <v>1.26</v>
@@ -1165,10 +1165,10 @@
         <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
         <v>42</v>
@@ -1198,7 +1198,7 @@
         <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
         <v>19</v>
@@ -1207,19 +1207,19 @@
         <v>15.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM3" t="n">
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO3" t="n">
         <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>25</v>
@@ -1240,10 +1240,10 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
         <v>9.6</v>
@@ -1255,19 +1255,19 @@
         <v>38</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
         <v>28</v>
@@ -1276,25 +1276,25 @@
         <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>70</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN3" t="n">
         <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
         <v>11</v>
@@ -1306,35 +1306,35 @@
         <v>19.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV3" t="n">
         <v>30</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA3" t="n">
         <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -1368,227 +1368,227 @@
         <v>1.86</v>
       </c>
       <c r="G4" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="H4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
         <v>2.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
         <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U4" t="n">
         <v>2.66</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
         <v>16.5</v>
       </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX4" t="n">
         <v>13</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF4" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ4" t="n">
         <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP4" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BR4" t="n">
         <v>21</v>
       </c>
       <c r="BS4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW4" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
         <v>70</v>
@@ -1688,7 +1688,7 @@
         <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>25</v>
@@ -1697,7 +1697,7 @@
         <v>230</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1706,43 +1706,43 @@
         <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="AJ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK5" t="n">
         <v>19</v>
       </c>
-      <c r="AK5" t="n">
-        <v>21</v>
-      </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
         <v>19.5</v>
@@ -1751,7 +1751,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
         <v>8.6</v>
@@ -1763,86 +1763,86 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>4.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="G6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="H6" t="n">
         <v>8.4</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.21</v>
@@ -1903,28 +1903,28 @@
         <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>1.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="X6" t="n">
         <v>95</v>
@@ -1951,19 +1951,19 @@
         <v>400</v>
       </c>
       <c r="AF6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK6" t="n">
         <v>14.5</v>
@@ -1975,22 +1975,22 @@
         <v>260</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AQ6" t="n">
         <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>12.5</v>
@@ -1999,10 +1999,10 @@
         <v>12.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
         <v>11.5</v>
@@ -2026,77 +2026,77 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>50</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>46</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
         <v>18</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT6" t="n">
         <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX6" t="n">
         <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.25</v>
       </c>
       <c r="G7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H7" t="n">
         <v>2.32</v>
@@ -2139,16 +2139,16 @@
         <v>2.44</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
         <v>3.7</v>
@@ -2157,7 +2157,7 @@
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>2.06</v>
@@ -2193,16 +2193,16 @@
         <v>34</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
         <v>11.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
         <v>25</v>
@@ -2229,7 +2229,7 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
         <v>22</v>
@@ -2244,7 +2244,7 @@
         <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -2268,89 +2268,89 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BC7" t="n">
         <v>32</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BG7" t="n">
         <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7" t="n">
         <v>10</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP7" t="n">
         <v>29</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR7" t="n">
         <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BU7" t="n">
         <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
         <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I8" t="n">
         <v>3.25</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.45</v>
@@ -2405,16 +2405,16 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
         <v>1.34</v>
@@ -2423,16 +2423,16 @@
         <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
         <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2444,7 +2444,7 @@
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
         <v>10</v>
@@ -2456,7 +2456,7 @@
         <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="n">
         <v>15</v>
@@ -2465,28 +2465,28 @@
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
         <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AP8" t="n">
         <v>12</v>
@@ -2498,7 +2498,7 @@
         <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT8" t="n">
         <v>9.4</v>
@@ -2510,10 +2510,10 @@
         <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB8" t="n">
         <v>30</v>
@@ -2534,22 +2534,22 @@
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BH8" t="n">
         <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
         <v>6.6</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.2</v>
@@ -2567,7 +2567,7 @@
         <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
@@ -2585,7 +2585,7 @@
         <v>5.6</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW8" t="n">
         <v>12</v>
@@ -2594,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>28</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I9" t="n">
         <v>3.8</v>
       </c>
-      <c r="I9" t="n">
-        <v>3.85</v>
-      </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
         <v>3.7</v>
@@ -2665,13 +2665,13 @@
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.98</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
         <v>3.55</v>
@@ -2680,16 +2680,16 @@
         <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
         <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
         <v>14.5</v>
@@ -2713,7 +2713,7 @@
         <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
@@ -2725,28 +2725,28 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
         <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO9" t="n">
         <v>46</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR9" t="n">
         <v>25</v>
@@ -2755,7 +2755,7 @@
         <v>65</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
@@ -2779,10 +2779,10 @@
         <v>48</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
         <v>30</v>
@@ -2791,10 +2791,10 @@
         <v>25</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH9" t="n">
         <v>3.4</v>
@@ -2806,10 +2806,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM9" t="n">
         <v>21</v>
@@ -2824,7 +2824,7 @@
         <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR9" t="n">
         <v>32</v>
@@ -2839,26 +2839,26 @@
         <v>6.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY9" t="n">
         <v>15</v>
       </c>
       <c r="BZ9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA9" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
@@ -2901,46 +2901,46 @@
         <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
         <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
@@ -2952,7 +2952,7 @@
         <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB10" t="n">
         <v>11.5</v>
@@ -2961,13 +2961,13 @@
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2976,13 +2976,13 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
         <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
         <v>44</v>
@@ -2994,19 +2994,19 @@
         <v>16.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3015,58 +3015,58 @@
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.7</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.7</v>
+        <v>38</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="BD10" t="n">
         <v>30</v>
       </c>
       <c r="BE10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
         <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.8</v>
@@ -3078,41 +3078,41 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
         <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -3146,16 +3146,16 @@
         <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H11" t="n">
         <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K11" t="n">
         <v>6.8</v>
@@ -3170,7 +3170,7 @@
         <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
         <v>2.3</v>
@@ -3179,22 +3179,22 @@
         <v>1.69</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
         <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
@@ -3209,7 +3209,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
         <v>15</v>
@@ -3218,10 +3218,10 @@
         <v>60</v>
       </c>
       <c r="AE11" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -3230,7 +3230,7 @@
         <v>40</v>
       </c>
       <c r="AI11" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ11" t="n">
         <v>9.800000000000001</v>
@@ -3242,37 +3242,37 @@
         <v>50</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>520</v>
+        <v>610</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
         <v>6.4</v>
@@ -3281,28 +3281,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>11.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="n">
         <v>4.2</v>
@@ -3311,62 +3311,62 @@
         <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>3.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BP11" t="n">
         <v>7.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>19</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
         <v>3.95</v>
@@ -3421,7 +3421,7 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
@@ -3430,7 +3430,7 @@
         <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
         <v>1.58</v>
@@ -3439,97 +3439,97 @@
         <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>15.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM12" t="n">
         <v>65</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AO12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW12" t="n">
         <v>28</v>
       </c>
-      <c r="AP12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>30</v>
-      </c>
       <c r="AX12" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
@@ -3538,89 +3538,89 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="n">
         <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL12" t="n">
         <v>85</v>
       </c>
       <c r="BM12" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW12" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BZ12" t="n">
         <v>17.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>3.2</v>
@@ -3675,13 +3675,13 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
         <v>2.36</v>
@@ -3690,145 +3690,145 @@
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
         <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
         <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
         <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
         <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
         <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="AX13" t="n">
         <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>65</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK13" t="n">
         <v>6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
@@ -3840,13 +3840,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR13" t="n">
         <v>38</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT13" t="n">
         <v>7</v>
@@ -3855,26 +3855,26 @@
         <v>6</v>
       </c>
       <c r="BV13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>38</v>
       </c>
       <c r="CA13" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G14" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="n">
         <v>2.48</v>
@@ -3923,43 +3923,43 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="U14" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="V14" t="n">
         <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y14" t="n">
         <v>18.5</v>
@@ -3980,64 +3980,64 @@
         <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
         <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
         <v>11.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>19.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
@@ -4058,10 +4058,10 @@
         <v>26</v>
       </c>
       <c r="BE14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG14" t="n">
         <v>10</v>
@@ -4070,65 +4070,65 @@
         <v>5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BJ14" t="n">
         <v>8.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO14" t="n">
         <v>5</v>
       </c>
       <c r="BP14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV14" t="n">
         <v>16</v>
       </c>
       <c r="BW14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY14" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA14" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
         <v>6.8</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>5.3</v>
@@ -4177,7 +4177,7 @@
         <v>5.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
@@ -4189,25 +4189,25 @@
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="S15" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
         <v>3</v>
@@ -4216,16 +4216,16 @@
         <v>36</v>
       </c>
       <c r="Y15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z15" t="n">
         <v>75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
         <v>13.5</v>
@@ -4258,16 +4258,16 @@
         <v>23</v>
       </c>
       <c r="AM15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ15" t="n">
         <v>36</v>
@@ -4279,13 +4279,13 @@
         <v>46</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU15" t="n">
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>65</v>
@@ -4294,13 +4294,13 @@
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB15" t="n">
         <v>13.5</v>
@@ -4315,28 +4315,28 @@
         <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH15" t="n">
         <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BM15" t="n">
-        <v>50</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN15" t="n">
         <v>4.8</v>
@@ -4348,41 +4348,41 @@
         <v>9</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS15" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BV15" t="n">
         <v>46</v>
       </c>
       <c r="BW15" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15" t="n">
         <v>42</v>
       </c>
       <c r="BY15" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="BZ15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>1.99</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
         <v>4.3</v>
@@ -4434,7 +4434,7 @@
         <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
         <v>4.6</v>
@@ -4443,7 +4443,7 @@
         <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
         <v>1.8</v>
@@ -4491,7 +4491,7 @@
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
@@ -4506,7 +4506,7 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>38</v>
@@ -4521,28 +4521,28 @@
         <v>50</v>
       </c>
       <c r="AP16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
         <v>15.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS16" t="n">
         <v>5.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -4557,7 +4557,7 @@
         <v>5.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>17</v>
@@ -4569,10 +4569,10 @@
         <v>5.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="BH16" t="n">
         <v>3.75</v>
@@ -4584,7 +4584,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>1.53</v>
       </c>
       <c r="G17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
         <v>6.6</v>
@@ -4682,34 +4682,34 @@
         <v>5.2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
         <v>2.58</v>
@@ -4718,7 +4718,7 @@
         <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X17" t="n">
         <v>34</v>
@@ -4730,7 +4730,7 @@
         <v>65</v>
       </c>
       <c r="AA17" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AB17" t="n">
         <v>15</v>
@@ -4754,13 +4754,13 @@
         <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
@@ -4769,43 +4769,43 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ17" t="n">
         <v>30</v>
       </c>
       <c r="AR17" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AS17" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AT17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU17" t="n">
         <v>11.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW17" t="n">
         <v>55</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY17" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
         <v>48</v>
@@ -4817,80 +4817,80 @@
         <v>12.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE17" t="n">
         <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI17" t="n">
         <v>4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BL17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM17" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO17" t="n">
         <v>4</v>
       </c>
       <c r="BP17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY17" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>11.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>10.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 07:13:43</t>
+          <t>2026-07-16 09:31:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,184 +857,184 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="K2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="L2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="M2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.16</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
         <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>1.65</v>
       </c>
       <c r="AS2" t="n">
-        <v>27</v>
+        <v>1.48</v>
       </c>
       <c r="AT2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY2" t="n">
         <v>6</v>
       </c>
-      <c r="AU2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>1.69</v>
       </c>
       <c r="BA2" t="n">
-        <v>19.5</v>
+        <v>1.48</v>
       </c>
       <c r="BB2" t="n">
-        <v>30</v>
+        <v>1.66</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>1.68</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>1.49</v>
       </c>
       <c r="BF2" t="n">
-        <v>36</v>
+        <v>1.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
@@ -1043,16 +1043,16 @@
         <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR2" t="n">
         <v>55</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
@@ -1061,16 +1061,16 @@
         <v>5.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="G3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
         <v>4.6</v>
@@ -1129,67 +1129,67 @@
         <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="S3" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1201,7 +1201,7 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
         <v>15.5</v>
@@ -1213,22 +1213,22 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AO3" t="n">
         <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AQ3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
@@ -1237,16 +1237,16 @@
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
@@ -1264,77 +1264,77 @@
         <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
         <v>28</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BR3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS3" t="n">
         <v>9.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA3" t="n">
         <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J4" t="n">
         <v>4.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
@@ -1395,109 +1395,109 @@
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Q4" t="n">
         <v>1.49</v>
       </c>
       <c r="R4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S4" t="n">
         <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U4" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
         <v>29</v>
       </c>
       <c r="Y4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
         <v>15.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
         <v>13.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
@@ -1506,89 +1506,89 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BH4" t="n">
         <v>5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BQ4" t="n">
         <v>5.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G5" t="n">
         <v>1.75</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I5" t="n">
         <v>7</v>
@@ -1634,31 +1634,31 @@
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
         <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
         <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
         <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
         <v>1.92</v>
@@ -1673,13 +1673,13 @@
         <v>2.32</v>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
         <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1691,7 +1691,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>230</v>
@@ -1706,7 +1706,7 @@
         <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="AJ5" t="n">
         <v>18</v>
@@ -1733,7 +1733,7 @@
         <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
         <v>9.199999999999999</v>
@@ -1745,7 +1745,7 @@
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
         <v>9.199999999999999</v>
@@ -1760,7 +1760,7 @@
         <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
         <v>14</v>
@@ -1769,16 +1769,16 @@
         <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -1873,136 +1873,136 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G6" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="R6" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="S6" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Y6" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="Z6" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="AA6" t="n">
         <v>270</v>
       </c>
       <c r="AB6" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AE6" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ6" t="n">
         <v>13.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL6" t="n">
         <v>27</v>
       </c>
       <c r="AM6" t="n">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AQ6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AS6" t="n">
         <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>12.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
         <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
         <v>11.5</v>
@@ -2026,77 +2026,77 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BQ6" t="n">
         <v>4.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU6" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX6" t="n">
         <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
         <v>2.32</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.44</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.35</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS7" t="n">
         <v>15</v>
       </c>
-      <c r="AH7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>22</v>
-      </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AX7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB7" t="n">
         <v>20</v>
       </c>
-      <c r="AY7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>38</v>
-      </c>
       <c r="BC7" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BE7" t="n">
-        <v>70</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX7" t="n">
         <v>42</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="BY7" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>8</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="CA7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
         <v>3.2</v>
@@ -2396,37 +2396,37 @@
         <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
         <v>1.44</v>
@@ -2435,19 +2435,19 @@
         <v>1.66</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
@@ -2456,7 +2456,7 @@
         <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
         <v>15</v>
@@ -2468,10 +2468,10 @@
         <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
         <v>27</v>
@@ -2480,7 +2480,7 @@
         <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="AN8" t="n">
         <v>25</v>
@@ -2498,7 +2498,7 @@
         <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
         <v>9.4</v>
@@ -2522,10 +2522,10 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC8" t="n">
         <v>24</v>
@@ -2534,7 +2534,7 @@
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF8" t="n">
         <v>22</v>
@@ -2552,59 +2552,59 @@
         <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM8" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO8" t="n">
         <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
         <v>25</v>
       </c>
       <c r="BW8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BZ8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I9" t="n">
         <v>3.75</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.6</v>
@@ -2665,10 +2665,10 @@
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
@@ -2677,28 +2677,28 @@
         <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="n">
         <v>9.6</v>
@@ -2707,28 +2707,28 @@
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>36</v>
@@ -2737,13 +2737,13 @@
         <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
         <v>13.5</v>
@@ -2752,7 +2752,7 @@
         <v>25</v>
       </c>
       <c r="AS9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT9" t="n">
         <v>9.199999999999999</v>
@@ -2767,7 +2767,7 @@
         <v>40</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2776,19 +2776,19 @@
         <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC9" t="n">
         <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
@@ -2806,31 +2806,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS9" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BT9" t="n">
         <v>6.8</v>
@@ -2839,26 +2839,26 @@
         <v>6.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW9" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="BX9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BZ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
         <v>4.4</v>
@@ -2907,70 +2907,70 @@
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
         <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
@@ -2979,13 +2979,13 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
@@ -2997,79 +2997,79 @@
         <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>75</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
         <v>38</v>
       </c>
       <c r="AX10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF10" t="n">
         <v>15</v>
       </c>
-      <c r="BA10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>14</v>
-      </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15.5</v>
+        <v>3.9</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO10" t="n">
         <v>4.3</v>
@@ -3078,41 +3078,41 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT10" t="n">
         <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA10" t="n">
         <v>12.5</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G11" t="n">
         <v>1.31</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
         <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.32</v>
@@ -3167,145 +3167,145 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
         <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Z11" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AE11" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
         <v>40</v>
       </c>
       <c r="AI11" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>530</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD11" t="n">
         <v>5.5</v>
       </c>
-      <c r="AO11" t="n">
-        <v>610</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="BE11" t="n">
         <v>6</v>
       </c>
-      <c r="AR11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD11" t="n">
+      <c r="BF11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG11" t="n">
         <v>6</v>
       </c>
-      <c r="BE11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF11" t="n">
+      <c r="BH11" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.2</v>
       </c>
       <c r="BI11" t="n">
         <v>3.3</v>
@@ -3323,10 +3323,10 @@
         <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BP11" t="n">
         <v>7.4</v>
@@ -3335,13 +3335,13 @@
         <v>5.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS11" t="n">
         <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BU11" t="n">
         <v>1.04</v>
@@ -3359,14 +3359,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA11" t="n">
         <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
         <v>1.32</v>
@@ -3427,16 +3427,16 @@
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
         <v>1.67</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
         <v>1.58</v>
@@ -3445,43 +3445,43 @@
         <v>2.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
         <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI12" t="n">
         <v>36</v>
@@ -3490,37 +3490,37 @@
         <v>32</v>
       </c>
       <c r="AK12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO12" t="n">
         <v>21</v>
       </c>
-      <c r="AL12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>23</v>
-      </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AT12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>12.5</v>
@@ -3529,64 +3529,64 @@
         <v>28</v>
       </c>
       <c r="AX12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
         <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BF12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.6</v>
       </c>
       <c r="BK12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN12" t="n">
         <v>5.9</v>
       </c>
-      <c r="BL12" t="n">
-        <v>85</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BO12" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BQ12" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BR12" t="n">
         <v>24</v>
@@ -3595,32 +3595,32 @@
         <v>16.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BW12" t="n">
         <v>17.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BY12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA12" t="n">
         <v>10.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -3669,34 +3669,34 @@
         <v>3.25</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P13" t="n">
         <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.92</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.93</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
@@ -3705,7 +3705,7 @@
         <v>1.77</v>
       </c>
       <c r="X13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
         <v>13.5</v>
@@ -3717,7 +3717,7 @@
         <v>90</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
@@ -3735,7 +3735,7 @@
         <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>80</v>
@@ -3801,22 +3801,22 @@
         <v>24</v>
       </c>
       <c r="BD13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE13" t="n">
         <v>100</v>
       </c>
       <c r="BF13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
@@ -3840,7 +3840,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR13" t="n">
         <v>38</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="H14" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="I14" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3941,49 +3941,49 @@
         <v>1.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.47</v>
       </c>
       <c r="U14" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
         <v>36</v>
       </c>
       <c r="AB14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC14" t="n">
         <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
@@ -3992,22 +3992,22 @@
         <v>13.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ14" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>11.5</v>
@@ -4019,25 +4019,25 @@
         <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT14" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU14" t="n">
         <v>9.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
@@ -4046,28 +4046,28 @@
         <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BF14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI14" t="n">
         <v>3.8</v>
@@ -4082,16 +4082,16 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BN14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BP14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ14" t="n">
         <v>13.5</v>
@@ -4103,10 +4103,10 @@
         <v>17</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV14" t="n">
         <v>16</v>
@@ -4118,17 +4118,17 @@
         <v>22</v>
       </c>
       <c r="BY14" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BZ14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H15" t="n">
         <v>6.8</v>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>5.3</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.24</v>
@@ -4189,25 +4189,25 @@
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
         <v>1.88</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
         <v>3</v>
@@ -4216,16 +4216,16 @@
         <v>36</v>
       </c>
       <c r="Y15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC15" t="n">
         <v>13.5</v>
@@ -4243,16 +4243,16 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
         <v>23</v>
@@ -4261,7 +4261,7 @@
         <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4270,10 +4270,10 @@
         <v>30</v>
       </c>
       <c r="AQ15" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS15" t="n">
         <v>46</v>
@@ -4285,7 +4285,7 @@
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
         <v>65</v>
@@ -4294,19 +4294,19 @@
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BB15" t="n">
         <v>13.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD15" t="n">
         <v>21</v>
@@ -4315,7 +4315,7 @@
         <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG15" t="n">
         <v>44</v>
@@ -4324,10 +4324,10 @@
         <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK15" t="n">
         <v>7.6</v>
@@ -4336,7 +4336,7 @@
         <v>80</v>
       </c>
       <c r="BM15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15" t="n">
         <v>4.8</v>
@@ -4345,7 +4345,7 @@
         <v>4</v>
       </c>
       <c r="BP15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ15" t="n">
         <v>6.8</v>
@@ -4354,7 +4354,7 @@
         <v>18.5</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT15" t="n">
         <v>11.5</v>
@@ -4363,26 +4363,26 @@
         <v>8.4</v>
       </c>
       <c r="BV15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA15" t="n">
         <v>7.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G16" t="n">
         <v>1.99</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.36</v>
@@ -4446,13 +4446,13 @@
         <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>1.71</v>
@@ -4461,25 +4461,25 @@
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
         <v>95</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
         <v>10.5</v>
@@ -4494,10 +4494,10 @@
         <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
@@ -4521,25 +4521,25 @@
         <v>50</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>15.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
         <v>38</v>
@@ -4548,13 +4548,13 @@
         <v>11.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.6</v>
+        <v>34</v>
       </c>
       <c r="BB16" t="n">
         <v>19</v>
@@ -4563,22 +4563,22 @@
         <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.199999999999999</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN16" t="n">
         <v>4.8</v>
@@ -4602,41 +4602,41 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR16" t="n">
         <v>25</v>
       </c>
       <c r="BS16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT16" t="n">
         <v>7.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
       </c>
       <c r="BW16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>19.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -4670,79 +4670,79 @@
         <v>1.53</v>
       </c>
       <c r="G17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="S17" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="U17" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
         <v>2.8</v>
       </c>
       <c r="X17" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y17" t="n">
         <v>36</v>
       </c>
       <c r="Z17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC17" t="n">
         <v>13</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
         <v>13</v>
@@ -4751,31 +4751,31 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP17" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AQ17" t="n">
         <v>30</v>
@@ -4787,110 +4787,110 @@
         <v>60</v>
       </c>
       <c r="AT17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>70</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN17" t="n">
         <v>4.7</v>
       </c>
-      <c r="BG17" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ17" t="n">
+      <c r="BO17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT17" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BK17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>80</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP17" t="n">
+      <c r="BU17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BQ17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BV17" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BW17" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BZ17" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -857,106 +857,106 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>3.35</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.92</v>
+        <v>2.12</v>
       </c>
       <c r="L2" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.17</v>
+        <v>1.59</v>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.61</v>
+        <v>3.75</v>
       </c>
       <c r="P2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S2" t="n">
+        <v>65</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.6</v>
-      </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>2.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>340</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>4.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AH2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -965,112 +965,112 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.6</v>
+        <v>2.58</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.65</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.48</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.68</v>
+        <v>300</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.5</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.69</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.48</v>
+        <v>330</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.66</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.65</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.68</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.49</v>
+        <v>21</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.55</v>
+        <v>350</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.55</v>
+        <v>310</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -1111,184 +1111,184 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="R3" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="T3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>16</v>
       </c>
       <c r="AI3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW3" t="n">
         <v>42</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AX3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AU3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13</v>
-      </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="BH3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="BN3" t="n">
         <v>4.9</v>
@@ -1297,44 +1297,44 @@
         <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ3" t="n">
         <v>9</v>
       </c>
       <c r="BR3" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BW3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>4.6</v>
       </c>
-      <c r="I4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.3</v>
-      </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1392,49 +1392,49 @@
         <v>6.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
         <v>1.51</v>
       </c>
       <c r="U4" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="X4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
         <v>21</v>
@@ -1443,19 +1443,19 @@
         <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>15.5</v>
@@ -1464,131 +1464,131 @@
         <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN4" t="n">
         <v>6.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR4" t="n">
         <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="AT4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU4" t="n">
         <v>10</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF4" t="n">
         <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BH4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI4" t="n">
         <v>3.9</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM4" t="n">
         <v>6.8</v>
       </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
         <v>55</v>
@@ -1685,164 +1685,164 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP5" t="n">
+      <c r="BG5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>12</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BR5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G6" t="n">
         <v>1.37</v>
       </c>
       <c r="H6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
         <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.2</v>
@@ -1897,25 +1897,25 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
         <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R6" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
         <v>2.28</v>
@@ -1924,16 +1924,16 @@
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="X6" t="n">
         <v>100</v>
       </c>
       <c r="Y6" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="Z6" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA6" t="n">
         <v>270</v>
@@ -1945,10 +1945,10 @@
         <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AE6" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="AF6" t="n">
         <v>12.5</v>
@@ -1972,22 +1972,22 @@
         <v>27</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP6" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
         <v>11</v>
@@ -1999,10 +1999,10 @@
         <v>12.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
         <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
         <v>11.5</v>
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>46</v>
+        <v>12.5</v>
       </c>
       <c r="BH6" t="n">
         <v>5.9</v>
@@ -2044,13 +2044,13 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
@@ -2062,31 +2062,31 @@
         <v>7.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR6" t="n">
         <v>17.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU6" t="n">
         <v>6</v>
       </c>
       <c r="BV6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX6" t="n">
         <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>8</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
         <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
         <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
         <v>11.5</v>
@@ -2187,7 +2187,7 @@
         <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA7" t="n">
         <v>36</v>
@@ -2211,28 +2211,28 @@
         <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
         <v>9.4</v>
@@ -2244,19 +2244,19 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
         <v>21</v>
@@ -2265,40 +2265,40 @@
         <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="BC7" t="n">
-        <v>19.5</v>
+        <v>38</v>
       </c>
       <c r="BD7" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,47 +2310,47 @@
         <v>7</v>
       </c>
       <c r="BO7" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>55</v>
       </c>
       <c r="BS7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>5.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BY7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA7" t="n">
         <v>8.4</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>44</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>8.6</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
         <v>3.2</v>
@@ -2393,46 +2393,46 @@
         <v>3.25</v>
       </c>
       <c r="J8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.45</v>
       </c>
-      <c r="K8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.14</v>
       </c>
       <c r="V8" t="n">
         <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
         <v>12.5</v>
@@ -2447,13 +2447,13 @@
         <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>38</v>
@@ -2468,28 +2468,28 @@
         <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
         <v>36</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
         <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2501,7 +2501,7 @@
         <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2510,7 +2510,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -2519,7 +2519,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
         <v>44</v>
@@ -2528,22 +2528,22 @@
         <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE8" t="n">
         <v>85</v>
       </c>
       <c r="BF8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI8" t="n">
         <v>3</v>
@@ -2552,31 +2552,31 @@
         <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM8" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP8" t="n">
         <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR8" t="n">
         <v>34</v>
       </c>
       <c r="BS8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BT8" t="n">
         <v>6.2</v>
@@ -2588,23 +2588,23 @@
         <v>25</v>
       </c>
       <c r="BW8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA8" t="n">
         <v>13</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>29</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>12</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -2635,28 +2635,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
         <v>3.9</v>
@@ -2665,67 +2665,67 @@
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.99</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
         <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="X9" t="n">
         <v>14</v>
       </c>
       <c r="Y9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD9" t="n">
         <v>14</v>
       </c>
-      <c r="Z9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>15</v>
-      </c>
       <c r="AE9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
         <v>23</v>
@@ -2737,128 +2737,128 @@
         <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP9" t="n">
         <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AS9" t="n">
         <v>60</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG9" t="n">
         <v>40</v>
       </c>
-      <c r="AX9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>42</v>
-      </c>
       <c r="BH9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL9" t="n">
         <v>120</v>
       </c>
       <c r="BM9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BN9" t="n">
         <v>5</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS9" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BW9" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
         <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
         <v>4.2</v>
@@ -2904,7 +2904,7 @@
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.44</v>
@@ -2913,34 +2913,34 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
         <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
         <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2961,10 +2961,10 @@
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
         <v>12.5</v>
@@ -2976,19 +2976,19 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
         <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AN10" t="n">
         <v>16.5</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AS10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
@@ -3027,7 +3027,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
         <v>55</v>
@@ -3042,13 +3042,13 @@
         <v>34</v>
       </c>
       <c r="BE10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="BF10" t="n">
         <v>15</v>
       </c>
       <c r="BG10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BH10" t="n">
         <v>3.25</v>
@@ -3084,13 +3084,13 @@
         <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT10" t="n">
         <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV10" t="n">
         <v>42</v>
@@ -3102,17 +3102,17 @@
         <v>46</v>
       </c>
       <c r="BY10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA10" t="n">
         <v>12.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -3143,37 +3143,37 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
         <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
         <v>1.65</v>
@@ -3182,13 +3182,13 @@
         <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
         <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
@@ -3203,88 +3203,88 @@
         <v>50</v>
       </c>
       <c r="Z11" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>16.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AE11" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AO11" t="n">
-        <v>530</v>
+        <v>490</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
         <v>7.8</v>
@@ -3293,25 +3293,25 @@
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="n">
         <v>4.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK11" t="n">
         <v>1.04</v>
@@ -3323,10 +3323,10 @@
         <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BP11" t="n">
         <v>7.4</v>
@@ -3335,7 +3335,7 @@
         <v>5.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
         <v>1.04</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -3397,46 +3397,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G12" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H12" t="n">
         <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
         <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
         <v>1.58</v>
@@ -3448,19 +3448,19 @@
         <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
         <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB12" t="n">
         <v>14.5</v>
@@ -3478,7 +3478,7 @@
         <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>14.5</v>
@@ -3487,10 +3487,10 @@
         <v>36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>30</v>
@@ -3499,16 +3499,16 @@
         <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>21</v>
       </c>
       <c r="AP12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR12" t="n">
         <v>21</v>
@@ -3517,16 +3517,16 @@
         <v>42</v>
       </c>
       <c r="AT12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -3538,13 +3538,13 @@
         <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
         <v>29</v>
       </c>
       <c r="BC12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>27</v>
@@ -3553,74 +3553,74 @@
         <v>42</v>
       </c>
       <c r="BF12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL12" t="n">
         <v>80</v>
       </c>
       <c r="BM12" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BO12" t="n">
         <v>5.1</v>
       </c>
       <c r="BP12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS12" t="n">
         <v>17</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BT12" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV12" t="n">
         <v>21</v>
       </c>
       <c r="BW12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BX12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY12" t="n">
         <v>21</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA12" t="n">
         <v>10.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -3654,70 +3654,70 @@
         <v>2.26</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
         <v>3.95</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
         <v>90</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
@@ -3735,7 +3735,7 @@
         <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>80</v>
@@ -3744,31 +3744,31 @@
         <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
         <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT13" t="n">
         <v>7.2</v>
@@ -3813,7 +3813,7 @@
         <v>50</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BI13" t="n">
         <v>2.68</v>
@@ -3822,13 +3822,13 @@
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN13" t="n">
         <v>5</v>
@@ -3840,13 +3840,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR13" t="n">
         <v>38</v>
       </c>
       <c r="BS13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT13" t="n">
         <v>7</v>
@@ -3858,23 +3858,23 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>38</v>
       </c>
       <c r="CA13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3923,7 +3923,7 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3935,16 +3935,16 @@
         <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R14" t="n">
         <v>1.79</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T14" t="n">
         <v>1.47</v>
@@ -3953,34 +3953,34 @@
         <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
         <v>30</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="n">
         <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF14" t="n">
         <v>24</v>
@@ -3998,7 +3998,7 @@
         <v>40</v>
       </c>
       <c r="AK14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
         <v>27</v>
@@ -4007,28 +4007,28 @@
         <v>44</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
         <v>26</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT14" t="n">
         <v>17.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV14" t="n">
         <v>11.5</v>
@@ -4037,7 +4037,7 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
@@ -4049,86 +4049,86 @@
         <v>24</v>
       </c>
       <c r="BB14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD14" t="n">
         <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM14" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO14" t="n">
         <v>5.7</v>
       </c>
       <c r="BP14" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BR14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS14" t="n">
-        <v>17</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV14" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BX14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY14" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA14" t="n">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
         <v>6.8</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>5.3</v>
@@ -4183,31 +4183,31 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
         <v>3</v>
@@ -4219,7 +4219,7 @@
         <v>38</v>
       </c>
       <c r="Z15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA15" t="n">
         <v>170</v>
@@ -4261,7 +4261,7 @@
         <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4270,13 +4270,13 @@
         <v>30</v>
       </c>
       <c r="AQ15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR15" t="n">
         <v>55</v>
       </c>
       <c r="AS15" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AT15" t="n">
         <v>13.5</v>
@@ -4315,74 +4315,74 @@
         <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BJ15" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BL15" t="n">
         <v>80</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
         <v>18.5</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BT15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BV15" t="n">
         <v>48</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX15" t="n">
         <v>44</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BZ15" t="n">
         <v>10</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>1.96</v>
       </c>
       <c r="G16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
@@ -4434,7 +4434,7 @@
         <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
         <v>4.6</v>
@@ -4449,19 +4449,19 @@
         <v>1.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
@@ -4494,16 +4494,16 @@
         <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
         <v>22</v>
@@ -4521,13 +4521,13 @@
         <v>50</v>
       </c>
       <c r="AP16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
         <v>15.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS16" t="n">
         <v>6.4</v>
@@ -4536,10 +4536,10 @@
         <v>9.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW16" t="n">
         <v>38</v>
@@ -4551,13 +4551,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
         <v>34</v>
       </c>
       <c r="BB16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC16" t="n">
         <v>17</v>
@@ -4599,10 +4599,10 @@
         <v>4.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR16" t="n">
         <v>25</v>
@@ -4611,16 +4611,16 @@
         <v>10.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV16" t="n">
         <v>32</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
         <v>5.3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -4691,46 +4691,46 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q17" t="n">
         <v>1.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
         <v>2.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X17" t="n">
         <v>38</v>
       </c>
       <c r="Y17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA17" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
         <v>15.5</v>
@@ -4739,10 +4739,10 @@
         <v>13</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
         <v>13</v>
@@ -4751,7 +4751,7 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
         <v>55</v>
@@ -4766,37 +4766,37 @@
         <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO17" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AP17" t="n">
         <v>32</v>
       </c>
       <c r="AQ17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AR17" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AS17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AT17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
@@ -4805,10 +4805,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -4817,80 +4817,80 @@
         <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH17" t="n">
         <v>5.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL17" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BM17" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BN17" t="n">
         <v>4.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BS17" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BV17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX17" t="n">
         <v>38</v>
       </c>
-      <c r="BW17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>36</v>
-      </c>
       <c r="BY17" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Vasco Da Gama</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I2" t="n">
         <v>4.6</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O2" t="n">
         <v>4.8</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.44</v>
+        <v>25</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
+        <v>90</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>490</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>520</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AT2" t="n">
         <v>5</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AU2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>270</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>220</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>480</v>
+      </c>
+      <c r="BB2" t="n">
         <v>150</v>
       </c>
-      <c r="AK2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>90</v>
-      </c>
       <c r="BC2" t="n">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="BD2" t="n">
-        <v>65</v>
+        <v>490</v>
       </c>
       <c r="BE2" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>85</v>
+        <v>370</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>200</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1102,49 +1102,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vasco Da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.56</v>
+        <v>3.45</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>2.06</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
@@ -1153,195 +1153,195 @@
         <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI3" t="n">
         <v>65</v>
       </c>
-      <c r="AB3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>50</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>360</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AS3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>2.64</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="BA3" t="n">
         <v>44</v>
       </c>
       <c r="BB3" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="BF3" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="BG3" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AC4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG4" t="n">
         <v>8</v>
       </c>
-      <c r="AD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10</v>
-      </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>330</v>
       </c>
       <c r="AN4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>510</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>18.5</v>
       </c>
-      <c r="AO4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>21</v>
-      </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BE4" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="BF4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>US MLS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>CF Montreal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Toronto FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="X5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP5" t="n">
         <v>13</v>
       </c>
-      <c r="Y5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB5" t="n">
         <v>30</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="BC5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE5" t="n">
         <v>90</v>
       </c>
-      <c r="AB5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="BF5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>600</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>65</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>90</v>
+      </c>
+      <c r="CA5" t="n">
         <v>55</v>
       </c>
-      <c r="AF5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>26</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>12</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1873,73 +1873,73 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G6" t="n">
         <v>1.29</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="I6" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="n">
         <v>55</v>
       </c>
       <c r="Z6" t="n">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="AA6" t="n">
-        <v>710</v>
+        <v>590</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
         <v>15.5</v>
@@ -1948,162 +1948,162 @@
         <v>55</v>
       </c>
       <c r="AE6" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
         <v>180</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AO6" t="n">
-        <v>420</v>
+        <v>270</v>
       </c>
       <c r="AP6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AR6" t="n">
         <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA6" t="n">
         <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE6" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM6" t="n">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BP6" t="n">
         <v>7.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BU6" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="CA6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="H7" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.05</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S7" t="n">
         <v>5.2</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.72</v>
-      </c>
       <c r="T7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.58</v>
       </c>
-      <c r="U7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.65</v>
-      </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AK7" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO7" t="n">
         <v>60</v>
       </c>
-      <c r="AN7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>21</v>
-      </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW7" t="n">
         <v>42</v>
       </c>
-      <c r="AT7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>27</v>
-      </c>
       <c r="AX7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>150</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV7" t="n">
         <v>30</v>
       </c>
-      <c r="BC7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>80</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>21</v>
-      </c>
       <c r="BW7" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="CA7" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US MLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:40:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="G8" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>2.64</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>2.96</v>
+        <v>6.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>2.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>2.14</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="Y8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AZ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="BG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.4</v>
+        <v>2.36</v>
       </c>
       <c r="BP8" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="BR8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>12.5</v>
+        <v>3.25</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>2.36</v>
       </c>
       <c r="BV8" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="BW8" t="n">
-        <v>12</v>
+        <v>3.1</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>14</v>
+        <v>3.25</v>
       </c>
       <c r="BZ8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.5</v>
+        <v>3.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:40:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St Louis City SC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.68</v>
+        <v>1.51</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>1.53</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>2.64</v>
+        <v>6.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="R9" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>2.88</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="Z9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV9" t="n">
         <v>23</v>
       </c>
-      <c r="AA9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AW9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY9" t="n">
         <v>10</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AZ9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>13</v>
       </c>
-      <c r="AE9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="BD9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX9" t="n">
         <v>40</v>
       </c>
-      <c r="AK9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BR9" t="n">
+      <c r="BY9" t="n">
         <v>22</v>
       </c>
-      <c r="BS9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>St Louis City SC</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="G10" t="n">
-        <v>1.49</v>
+        <v>1.99</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="R10" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="n">
-        <v>38</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AA10" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AK10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>24</v>
-      </c>
       <c r="AW10" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP10" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>80</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BS10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BW10" t="n">
         <v>12.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BY10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>US MLS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,228 +3129,228 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>23:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlante</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="H11" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.5</v>
+        <v>38</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY11" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BE11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM11" t="n">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO11" t="n">
         <v>4.3</v>
       </c>
       <c r="BP11" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ11" t="n">
         <v>8</v>
       </c>
       <c r="BR11" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV11" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BW11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BX11" t="n">
         <v>38</v>
@@ -3359,268 +3359,14 @@
         <v>13</v>
       </c>
       <c r="BZ11" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>23:30:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="X12" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>38</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>75</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
